--- a/origin/SWMM2AI-Experiment-master1/Actual Rainfall_Water Level/2024-2-3.xlsx
+++ b/origin/SWMM2AI-Experiment-master1/Actual Rainfall_Water Level/2024-2-3.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView windowWidth="21942" windowHeight="9805"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="R20240202" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>时间</t>
   </si>
@@ -35,375 +22,51 @@
     <t>雨强(mm/hr)</t>
   </si>
   <si>
-    <t>液位</t>
+    <t>HUZU_STORM_L_01_液位</t>
+  </si>
+  <si>
+    <t>HUZU_WASTE_L_01_液位</t>
+  </si>
+  <si>
+    <t>HUZU_WASTE_L_02_液位</t>
+  </si>
+  <si>
+    <t>HUZU_STORM_L_02_液位</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d\ hh:mm;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -413,314 +76,35 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -735,39 +119,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -799,7 +183,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -834,7 +217,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -846,3330 +228,5955 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C289"/>
-  <sheetFormatPr defaultColWidth="9.72972972972973" defaultRowHeight="14.1" outlineLevelCol="2"/>
-  <cols>
-    <col min="1" max="1" width="31.1981981981982" customWidth="1"/>
-    <col min="3" max="3" width="9.72972972972973" style="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F289"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>45325</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>0.19</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>1.362</v>
+      </c>
+      <c r="E2">
+        <v>0.705</v>
+      </c>
+      <c r="F2">
+        <v>0.097</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>45325.0034722222</v>
+        <v>45325.00347222222</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>0.192</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>1.364</v>
+      </c>
+      <c r="E3">
+        <v>0.708</v>
+      </c>
+      <c r="F3">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>45325.0069444444</v>
+        <v>45325.00694444445</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>0.192</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <v>1.364</v>
+      </c>
+      <c r="E4">
+        <v>0.706</v>
+      </c>
+      <c r="F4">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>45325.0104166667</v>
+        <v>45325.01041666666</v>
       </c>
       <c r="B5">
         <v>9.6</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>0.194</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <v>1.366</v>
+      </c>
+      <c r="E5">
+        <v>0.709</v>
+      </c>
+      <c r="F5">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>45325.0138888889</v>
+        <v>45325.01388888889</v>
       </c>
       <c r="B6">
         <v>7.2</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>0.206</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6">
+        <v>1.378</v>
+      </c>
+      <c r="E6">
+        <v>0.711</v>
+      </c>
+      <c r="F6">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>45325.0173611111</v>
+        <v>45325.01736111111</v>
       </c>
       <c r="B7">
         <v>4.8</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>0.206</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7">
+        <v>1.378</v>
+      </c>
+      <c r="E7">
+        <v>0.721</v>
+      </c>
+      <c r="F7">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>45325.0208333333</v>
+        <v>45325.02083333334</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8">
         <v>0.209</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8">
+        <v>1.381</v>
+      </c>
+      <c r="E8">
+        <v>0.724</v>
+      </c>
+      <c r="F8">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>45325.0243055556</v>
+        <v>45325.02430555555</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9">
         <v>0.209</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9">
+        <v>1.381</v>
+      </c>
+      <c r="E9">
+        <v>0.724</v>
+      </c>
+      <c r="F9">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>45325.0277777778</v>
+        <v>45325.02777777778</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10">
         <v>0.209</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10">
+        <v>1.381</v>
+      </c>
+      <c r="E10">
+        <v>0.725</v>
+      </c>
+      <c r="F10">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2">
         <v>45325.03125</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>0.208</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11">
+        <v>1.38</v>
+      </c>
+      <c r="E11">
+        <v>0.724</v>
+      </c>
+      <c r="F11">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>45325.0347222222</v>
+        <v>45325.03472222222</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <v>0.209</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12">
+        <v>1.38</v>
+      </c>
+      <c r="E12">
+        <v>0.723</v>
+      </c>
+      <c r="F12">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>45325.0381944444</v>
+        <v>45325.03819444445</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13">
         <v>0.207</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13">
+        <v>1.379</v>
+      </c>
+      <c r="E13">
+        <v>0.722</v>
+      </c>
+      <c r="F13">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>45325.0416666667</v>
+        <v>45325.04166666666</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14">
         <v>0.207</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14">
+        <v>1.379</v>
+      </c>
+      <c r="E14">
+        <v>0.722</v>
+      </c>
+      <c r="F14">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>45325.0451388889</v>
+        <v>45325.04513888889</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <v>0.212</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15">
+        <v>1.387</v>
+      </c>
+      <c r="E15">
+        <v>0.721</v>
+      </c>
+      <c r="F15">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>45325.0486111111</v>
+        <v>45325.04861111111</v>
       </c>
       <c r="B16">
         <v>2.4</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16">
         <v>0.208</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16">
+        <v>1.379</v>
+      </c>
+      <c r="E16">
+        <v>0.719</v>
+      </c>
+      <c r="F16">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>45325.0520833333</v>
+        <v>45325.05208333334</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17">
         <v>0.209</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17">
+        <v>1.387</v>
+      </c>
+      <c r="E17">
+        <v>0.73</v>
+      </c>
+      <c r="F17">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>45325.0555555556</v>
+        <v>45325.05555555555</v>
       </c>
       <c r="B18">
         <v>2.4</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18">
         <v>0.207</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18">
+        <v>1.379</v>
+      </c>
+      <c r="E18">
+        <v>0.722</v>
+      </c>
+      <c r="F18">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>45325.0590277778</v>
+        <v>45325.05902777778</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19">
         <v>0.21</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19">
+        <v>1.392</v>
+      </c>
+      <c r="E19">
+        <v>0.725</v>
+      </c>
+      <c r="F19">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2">
         <v>45325.0625</v>
       </c>
       <c r="B20">
         <v>4.8</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20">
         <v>0.209</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20">
+        <v>1.384</v>
+      </c>
+      <c r="E20">
+        <v>0.723</v>
+      </c>
+      <c r="F20">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>45325.0659722222</v>
+        <v>45325.06597222222</v>
       </c>
       <c r="B21">
         <v>2.4</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21">
         <v>0.211</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21">
+        <v>1.392</v>
+      </c>
+      <c r="E21">
+        <v>0.726</v>
+      </c>
+      <c r="F21">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>45325.0694444444</v>
+        <v>45325.06944444445</v>
       </c>
       <c r="B22">
         <v>7.2</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22">
         <v>0.214</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22">
+        <v>1.4</v>
+      </c>
+      <c r="E22">
+        <v>0.732</v>
+      </c>
+      <c r="F22">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>45325.0729166667</v>
+        <v>45325.07291666666</v>
       </c>
       <c r="B23">
         <v>2.4</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23">
         <v>0.221</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23">
+        <v>1.402</v>
+      </c>
+      <c r="E23">
+        <v>0.735</v>
+      </c>
+      <c r="F23">
+        <v>0.131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>45325.0763888889</v>
+        <v>45325.07638888889</v>
       </c>
       <c r="B24">
         <v>9.6</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24">
         <v>0.232</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24">
+        <v>1.404</v>
+      </c>
+      <c r="E24">
+        <v>0.747</v>
+      </c>
+      <c r="F24">
+        <v>0.143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>45325.0798611111</v>
+        <v>45325.07986111111</v>
       </c>
       <c r="B25">
         <v>7.2</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25">
         <v>0.233</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25">
+        <v>1.415</v>
+      </c>
+      <c r="E25">
+        <v>0.751</v>
+      </c>
+      <c r="F25">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>45325.0833333333</v>
+        <v>45325.08333333334</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26">
+        <v>1.419</v>
+      </c>
+      <c r="E26">
+        <v>0.756</v>
+      </c>
+      <c r="F26">
+        <v>0.138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>45325.0868055556</v>
+        <v>45325.08680555555</v>
       </c>
       <c r="B27">
         <v>4.8</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27">
+        <v>1.416</v>
+      </c>
+      <c r="E27">
+        <v>0.758</v>
+      </c>
+      <c r="F27">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>45325.0902777778</v>
+        <v>45325.09027777778</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28">
         <v>0.223</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28">
+        <v>1.415</v>
+      </c>
+      <c r="E28">
+        <v>0.758</v>
+      </c>
+      <c r="F28">
+        <v>0.133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="2">
         <v>45325.09375</v>
       </c>
       <c r="B29">
         <v>2.4</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29">
         <v>0.223</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29">
+        <v>1.415</v>
+      </c>
+      <c r="E29">
+        <v>0.758</v>
+      </c>
+      <c r="F29">
+        <v>0.134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>45325.0972222222</v>
+        <v>45325.09722222222</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30">
         <v>0.226</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30">
+        <v>1.418</v>
+      </c>
+      <c r="E30">
+        <v>0.761</v>
+      </c>
+      <c r="F30">
+        <v>0.133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>45325.1006944444</v>
+        <v>45325.10069444445</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31">
         <v>0.225</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31">
+        <v>1.417</v>
+      </c>
+      <c r="E31">
+        <v>0.753</v>
+      </c>
+      <c r="F31">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>45325.1041666667</v>
+        <v>45325.10416666666</v>
       </c>
       <c r="B32">
         <v>2.4</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32">
         <v>0.227</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32">
+        <v>1.419</v>
+      </c>
+      <c r="E32">
+        <v>0.761</v>
+      </c>
+      <c r="F32">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>45325.1076388889</v>
+        <v>45325.10763888889</v>
       </c>
       <c r="B33">
         <v>2.4</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33">
         <v>0.226</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33">
+        <v>1.414</v>
+      </c>
+      <c r="E33">
+        <v>0.75</v>
+      </c>
+      <c r="F33">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>45325.1111111111</v>
+        <v>45325.11111111111</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34">
         <v>0.226</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34">
+        <v>1.418</v>
+      </c>
+      <c r="E34">
+        <v>0.751</v>
+      </c>
+      <c r="F34">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>45325.1145833333</v>
+        <v>45325.11458333334</v>
       </c>
       <c r="B35">
         <v>2.4</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35">
         <v>0.225</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35">
+        <v>1.417</v>
+      </c>
+      <c r="E35">
+        <v>0.753</v>
+      </c>
+      <c r="F35">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>45325.1180555556</v>
+        <v>45325.11805555555</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36">
         <v>0.227</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36">
+        <v>1.419</v>
+      </c>
+      <c r="E36">
+        <v>0.752</v>
+      </c>
+      <c r="F36">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>45325.1215277778</v>
+        <v>45325.12152777778</v>
       </c>
       <c r="B37">
         <v>2.4</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37">
         <v>0.22</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37">
+        <v>1.412</v>
+      </c>
+      <c r="E37">
+        <v>0.755</v>
+      </c>
+      <c r="F37">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="2">
         <v>45325.125</v>
       </c>
       <c r="B38">
         <v>2.4</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38">
         <v>0.22</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38">
+        <v>1.413</v>
+      </c>
+      <c r="E38">
+        <v>0.755</v>
+      </c>
+      <c r="F38">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>45325.1284722222</v>
+        <v>45325.12847222222</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39">
         <v>0.22</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D39">
+        <v>1.412</v>
+      </c>
+      <c r="E39">
+        <v>0.752</v>
+      </c>
+      <c r="F39">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>45325.1319444444</v>
+        <v>45325.13194444445</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40">
         <v>0.225</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="D40">
+        <v>1.41</v>
+      </c>
+      <c r="E40">
+        <v>0.753</v>
+      </c>
+      <c r="F40">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>45325.1354166667</v>
+        <v>45325.13541666666</v>
       </c>
       <c r="B41">
         <v>4.8</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41">
         <v>0.231</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41">
+        <v>1.413</v>
+      </c>
+      <c r="E41">
+        <v>0.755</v>
+      </c>
+      <c r="F41">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>45325.1388888889</v>
+        <v>45325.13888888889</v>
       </c>
       <c r="B42">
         <v>4.8</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42">
         <v>0.231</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="D42">
+        <v>1.422</v>
+      </c>
+      <c r="E42">
+        <v>0.756</v>
+      </c>
+      <c r="F42">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>45325.1423611111</v>
+        <v>45325.14236111111</v>
       </c>
       <c r="B43">
         <v>7.2</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43">
         <v>0.234</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="D43">
+        <v>1.422</v>
+      </c>
+      <c r="E43">
+        <v>0.762</v>
+      </c>
+      <c r="F43">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>45325.1458333333</v>
+        <v>45325.14583333334</v>
       </c>
       <c r="B44">
         <v>2.4</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44">
         <v>0.236</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="D44">
+        <v>1.431</v>
+      </c>
+      <c r="E44">
+        <v>0.764</v>
+      </c>
+      <c r="F44">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>45325.1493055556</v>
+        <v>45325.14930555555</v>
       </c>
       <c r="B45">
         <v>4.8</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45">
         <v>0.234</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="D45">
+        <v>1.436</v>
+      </c>
+      <c r="E45">
+        <v>0.773</v>
+      </c>
+      <c r="F45">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>45325.1527777778</v>
+        <v>45325.15277777778</v>
       </c>
       <c r="B46">
         <v>4.8</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46">
         <v>0.236</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="D46">
+        <v>1.431</v>
+      </c>
+      <c r="E46">
+        <v>0.771</v>
+      </c>
+      <c r="F46">
+        <v>0.143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="2">
         <v>45325.15625</v>
       </c>
       <c r="B47">
         <v>4.8</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47">
         <v>0.241</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="D47">
+        <v>1.443</v>
+      </c>
+      <c r="E47">
+        <v>0.775</v>
+      </c>
+      <c r="F47">
+        <v>0.147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>45325.1597222222</v>
+        <v>45325.15972222222</v>
       </c>
       <c r="B48">
         <v>12</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48">
         <v>0.254</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="D48">
+        <v>1.446</v>
+      </c>
+      <c r="E48">
+        <v>0.789</v>
+      </c>
+      <c r="F48">
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>45325.1631944444</v>
+        <v>45325.16319444445</v>
       </c>
       <c r="B49">
         <v>12</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49">
         <v>0.272</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="D49">
+        <v>1.464</v>
+      </c>
+      <c r="E49">
+        <v>0.797</v>
+      </c>
+      <c r="F49">
+        <v>0.169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>45325.1666666667</v>
+        <v>45325.16666666666</v>
       </c>
       <c r="B50">
         <v>9.6</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50">
         <v>0.265</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="D50">
+        <v>1.471</v>
+      </c>
+      <c r="E50">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="F50">
+        <v>0.165</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>45325.1701388889</v>
+        <v>45325.17013888889</v>
       </c>
       <c r="B51">
         <v>7.2</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="D51">
+        <v>1.466</v>
+      </c>
+      <c r="E51">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="F51">
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>45325.1736111111</v>
+        <v>45325.17361111111</v>
       </c>
       <c r="B52">
         <v>12</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52">
         <v>0.272</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="D52">
+        <v>1.474</v>
+      </c>
+      <c r="E52">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="F52">
+        <v>0.169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>45325.1770833333</v>
+        <v>45325.17708333334</v>
       </c>
       <c r="B53">
         <v>9.6</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53">
         <v>0.276</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="D53">
+        <v>1.477</v>
+      </c>
+      <c r="E53">
+        <v>0.819</v>
+      </c>
+      <c r="F53">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>45325.1805555556</v>
+        <v>45325.18055555555</v>
       </c>
       <c r="B54">
         <v>14.4</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54">
         <v>0.282</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="D54">
+        <v>1.485</v>
+      </c>
+      <c r="E54">
+        <v>0.828</v>
+      </c>
+      <c r="F54">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>45325.1840277778</v>
+        <v>45325.18402777778</v>
       </c>
       <c r="B55">
         <v>7.2</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55">
         <v>0.273</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="D55">
+        <v>1.489</v>
+      </c>
+      <c r="E55">
+        <v>0.832</v>
+      </c>
+      <c r="F55">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="2">
         <v>45325.1875</v>
       </c>
       <c r="B56">
         <v>2.4</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56">
         <v>0.266</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="D56">
+        <v>1.489</v>
+      </c>
+      <c r="E56">
+        <v>0.822</v>
+      </c>
+      <c r="F56">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>45325.1909722222</v>
+        <v>45325.19097222222</v>
       </c>
       <c r="B57">
         <v>2.4</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57">
         <v>0.268</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="D57">
+        <v>1.48</v>
+      </c>
+      <c r="E57">
+        <v>0.825</v>
+      </c>
+      <c r="F57">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>45325.1944444444</v>
+        <v>45325.19444444445</v>
       </c>
       <c r="B58">
         <v>2.4</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="D58">
+        <v>1.482</v>
+      </c>
+      <c r="E58">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="F58">
+        <v>0.147</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>45325.1979166667</v>
+        <v>45325.19791666666</v>
       </c>
       <c r="B59">
         <v>4.8</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59">
         <v>0.262</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="D59">
+        <v>1.474</v>
+      </c>
+      <c r="E59">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="F59">
+        <v>0.148</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>45325.2013888889</v>
+        <v>45325.20138888889</v>
       </c>
       <c r="B60">
         <v>4.8</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60">
         <v>0.268</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="D60">
+        <v>1.48</v>
+      </c>
+      <c r="E60">
+        <v>0.823</v>
+      </c>
+      <c r="F60">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>45325.2048611111</v>
+        <v>45325.20486111111</v>
       </c>
       <c r="B61">
         <v>9.6</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61">
         <v>0.276</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="D61">
+        <v>1.489</v>
+      </c>
+      <c r="E61">
+        <v>0.828</v>
+      </c>
+      <c r="F61">
+        <v>0.163</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>45325.2083333333</v>
+        <v>45325.20833333334</v>
       </c>
       <c r="B62">
         <v>7.2</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C62">
         <v>0.273</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="D62">
+        <v>1.496</v>
+      </c>
+      <c r="E62">
+        <v>0.828</v>
+      </c>
+      <c r="F62">
+        <v>0.159</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>45325.2118055556</v>
+        <v>45325.21180555555</v>
       </c>
       <c r="B63">
         <v>2.4</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63">
         <v>0.273</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="D63">
+        <v>1.496</v>
+      </c>
+      <c r="E63">
+        <v>0.828</v>
+      </c>
+      <c r="F63">
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>45325.2152777778</v>
+        <v>45325.21527777778</v>
       </c>
       <c r="B64">
         <v>2.4</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64">
         <v>0.269</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="D64">
+        <v>1.492</v>
+      </c>
+      <c r="E64">
+        <v>0.831</v>
+      </c>
+      <c r="F64">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" s="2">
         <v>45325.21875</v>
       </c>
       <c r="B65">
         <v>2.4</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65">
         <v>0.275</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="D65">
+        <v>1.487</v>
+      </c>
+      <c r="E65">
+        <v>0.831</v>
+      </c>
+      <c r="F65">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>45325.2222222222</v>
+        <v>45325.22222222222</v>
       </c>
       <c r="B66">
         <v>4.8</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66">
         <v>0.274</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="D66">
+        <v>1.487</v>
+      </c>
+      <c r="E66">
+        <v>0.83</v>
+      </c>
+      <c r="F66">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>45325.2256944444</v>
+        <v>45325.22569444445</v>
       </c>
       <c r="B67">
         <v>4.8</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67">
         <v>0.279</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="D67">
+        <v>1.491</v>
+      </c>
+      <c r="E67">
+        <v>0.828</v>
+      </c>
+      <c r="F67">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>45325.2291666667</v>
+        <v>45325.22916666666</v>
       </c>
       <c r="B68">
         <v>7.2</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68">
         <v>0.281</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="D68">
+        <v>1.493</v>
+      </c>
+      <c r="E68">
+        <v>0.836</v>
+      </c>
+      <c r="F68">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>45325.2326388889</v>
+        <v>45325.23263888889</v>
       </c>
       <c r="B69">
         <v>4.8</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69">
         <v>0.28</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="D69">
+        <v>1.493</v>
+      </c>
+      <c r="E69">
+        <v>0.836</v>
+      </c>
+      <c r="F69">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>45325.2361111111</v>
+        <v>45325.23611111111</v>
       </c>
       <c r="B70">
         <v>7.2</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70">
         <v>0.288</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="D70">
+        <v>1.5</v>
+      </c>
+      <c r="E70">
+        <v>0.842</v>
+      </c>
+      <c r="F70">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>45325.2395833333</v>
+        <v>45325.23958333334</v>
       </c>
       <c r="B71">
         <v>14.4</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71">
         <v>0.292</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="D71">
+        <v>1.515</v>
+      </c>
+      <c r="E71">
+        <v>0.854</v>
+      </c>
+      <c r="F71">
+        <v>0.179</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>45325.2430555556</v>
+        <v>45325.24305555555</v>
       </c>
       <c r="B72">
         <v>4.8</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72">
         <v>0.292</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="D72">
+        <v>1.515</v>
+      </c>
+      <c r="E72">
+        <v>0.857</v>
+      </c>
+      <c r="F72">
+        <v>0.169</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>45325.2465277778</v>
+        <v>45325.24652777778</v>
       </c>
       <c r="B73">
         <v>4.8</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C73">
         <v>0.292</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
+      <c r="D73">
+        <v>1.515</v>
+      </c>
+      <c r="E73">
+        <v>0.858</v>
+      </c>
+      <c r="F73">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="2">
         <v>45325.25</v>
       </c>
       <c r="B74">
         <v>7.2</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74">
         <v>0.288</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="D74">
+        <v>1.518</v>
+      </c>
+      <c r="E74">
+        <v>0.854</v>
+      </c>
+      <c r="F74">
+        <v>0.165</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>45325.2534722222</v>
+        <v>45325.25347222222</v>
       </c>
       <c r="B75">
         <v>7.2</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75">
         <v>0.297</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="D75">
+        <v>1.519</v>
+      </c>
+      <c r="E75">
+        <v>0.851</v>
+      </c>
+      <c r="F75">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>45325.2569444444</v>
+        <v>45325.25694444445</v>
       </c>
       <c r="B76">
         <v>2.4</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76">
         <v>0.291</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="D76">
+        <v>1.514</v>
+      </c>
+      <c r="E76">
+        <v>0.856</v>
+      </c>
+      <c r="F76">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>45325.2604166667</v>
+        <v>45325.26041666666</v>
       </c>
       <c r="B77">
         <v>2.4</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C77">
         <v>0.291</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
+      <c r="D77">
+        <v>1.514</v>
+      </c>
+      <c r="E77">
+        <v>0.857</v>
+      </c>
+      <c r="F77">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>45325.2638888889</v>
+        <v>45325.26388888889</v>
       </c>
       <c r="B78">
         <v>2.4</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78">
         <v>0.298</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
+      <c r="D78">
+        <v>1.51</v>
+      </c>
+      <c r="E78">
+        <v>0.853</v>
+      </c>
+      <c r="F78">
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>45325.2673611111</v>
+        <v>45325.26736111111</v>
       </c>
       <c r="B79">
         <v>7.2</v>
       </c>
-      <c r="C79" s="1">
+      <c r="C79">
         <v>0.295</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="D79">
+        <v>1.514</v>
+      </c>
+      <c r="E79">
+        <v>0.851</v>
+      </c>
+      <c r="F79">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>45325.2708333333</v>
+        <v>45325.27083333334</v>
       </c>
       <c r="B80">
         <v>4.8</v>
       </c>
-      <c r="C80" s="1">
+      <c r="C80">
         <v>0.295</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="D80">
+        <v>1.518</v>
+      </c>
+      <c r="E80">
+        <v>0.851</v>
+      </c>
+      <c r="F80">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>45325.2743055556</v>
+        <v>45325.27430555555</v>
       </c>
       <c r="B81">
         <v>4.8</v>
       </c>
-      <c r="C81" s="1">
+      <c r="C81">
         <v>0.301</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="D81">
+        <v>1.521</v>
+      </c>
+      <c r="E81">
+        <v>0.866</v>
+      </c>
+      <c r="F81">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>45325.2777777778</v>
+        <v>45325.27777777778</v>
       </c>
       <c r="B82">
         <v>2.4</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C82">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="D82">
+        <v>1.513</v>
+      </c>
+      <c r="E82">
+        <v>0.857</v>
+      </c>
+      <c r="F82">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" s="2">
         <v>45325.28125</v>
       </c>
       <c r="B83">
         <v>2.4</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C83">
         <v>0.299</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="D83">
+        <v>1.511</v>
+      </c>
+      <c r="E83">
+        <v>0.855</v>
+      </c>
+      <c r="F83">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>45325.2847222222</v>
+        <v>45325.28472222222</v>
       </c>
       <c r="B84">
         <v>4.8</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C84">
         <v>0.298</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="D84">
+        <v>1.51</v>
+      </c>
+      <c r="E84">
+        <v>0.853</v>
+      </c>
+      <c r="F84">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>45325.2881944444</v>
+        <v>45325.28819444445</v>
       </c>
       <c r="B85">
         <v>2.4</v>
       </c>
-      <c r="C85" s="1">
+      <c r="C85">
         <v>0.296</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="D85">
+        <v>1.516</v>
+      </c>
+      <c r="E85">
+        <v>0.851</v>
+      </c>
+      <c r="F85">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>45325.2916666667</v>
+        <v>45325.29166666666</v>
       </c>
       <c r="B86">
         <v>2.4</v>
       </c>
-      <c r="C86" s="1">
+      <c r="C86">
         <v>0.298</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="D86">
+        <v>1.511</v>
+      </c>
+      <c r="E86">
+        <v>0.853</v>
+      </c>
+      <c r="F86">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>45325.2951388889</v>
+        <v>45325.29513888889</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C87">
         <v>0.294</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="D87">
+        <v>1.506</v>
+      </c>
+      <c r="E87">
+        <v>0.848</v>
+      </c>
+      <c r="F87">
+        <v>0.139</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>45325.2986111111</v>
+        <v>45325.29861111111</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C88">
         <v>0.293</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="D88">
+        <v>1.516</v>
+      </c>
+      <c r="E88">
+        <v>0.849</v>
+      </c>
+      <c r="F88">
+        <v>0.139</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>45325.3020833333</v>
+        <v>45325.30208333334</v>
       </c>
       <c r="B89">
         <v>2.4</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C89">
         <v>0.293</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="D89">
+        <v>1.502</v>
+      </c>
+      <c r="E89">
+        <v>0.846</v>
+      </c>
+      <c r="F89">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>45325.3055555556</v>
+        <v>45325.30555555555</v>
       </c>
       <c r="B90">
         <v>2.4</v>
       </c>
-      <c r="C90" s="1">
+      <c r="C90">
         <v>0.297</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="D90">
+        <v>1.503</v>
+      </c>
+      <c r="E90">
+        <v>0.846</v>
+      </c>
+      <c r="F90">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>45325.3090277778</v>
+        <v>45325.30902777778</v>
       </c>
       <c r="B91">
         <v>2.4</v>
       </c>
-      <c r="C91" s="1">
+      <c r="C91">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="D91">
+        <v>1.503</v>
+      </c>
+      <c r="E91">
+        <v>0.842</v>
+      </c>
+      <c r="F91">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" s="2">
         <v>45325.3125</v>
       </c>
       <c r="B92">
         <v>2.4</v>
       </c>
-      <c r="C92" s="1">
+      <c r="C92">
         <v>0.289</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="D92">
+        <v>1.501</v>
+      </c>
+      <c r="E92">
+        <v>0.845</v>
+      </c>
+      <c r="F92">
+        <v>0.138</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>45325.3159722222</v>
+        <v>45325.31597222222</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
-      <c r="C93" s="1">
+      <c r="C93">
         <v>0.299</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="D93">
+        <v>1.501</v>
+      </c>
+      <c r="E93">
+        <v>0.84</v>
+      </c>
+      <c r="F93">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>45325.3194444444</v>
+        <v>45325.31944444445</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
-      <c r="C94" s="1">
+      <c r="C94">
         <v>0.298</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="D94">
+        <v>1.501</v>
+      </c>
+      <c r="E94">
+        <v>0.834</v>
+      </c>
+      <c r="F94">
+        <v>0.134</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>45325.3229166667</v>
+        <v>45325.32291666666</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
-      <c r="C95" s="1">
+      <c r="C95">
         <v>0.297</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
+      <c r="D95">
+        <v>1.5</v>
+      </c>
+      <c r="E95">
+        <v>0.832</v>
+      </c>
+      <c r="F95">
+        <v>0.133</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>45325.3263888889</v>
+        <v>45325.32638888889</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
-      <c r="C96" s="1">
+      <c r="C96">
         <v>0.295</v>
       </c>
-    </row>
-    <row r="97" spans="1:3">
+      <c r="D96">
+        <v>1.497</v>
+      </c>
+      <c r="E96">
+        <v>0.831</v>
+      </c>
+      <c r="F96">
+        <v>0.131</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>45325.3298611111</v>
+        <v>45325.32986111111</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
-      <c r="C97" s="1">
+      <c r="C97">
         <v>0.291</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
+      <c r="D97">
+        <v>1.493</v>
+      </c>
+      <c r="E97">
+        <v>0.826</v>
+      </c>
+      <c r="F97">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>45325.3333333333</v>
+        <v>45325.33333333334</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C98">
         <v>0.292</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
+      <c r="D98">
+        <v>1.495</v>
+      </c>
+      <c r="E98">
+        <v>0.827</v>
+      </c>
+      <c r="F98">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>45325.3368055556</v>
+        <v>45325.33680555555</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
-      <c r="C99" s="1">
+      <c r="C99">
         <v>0.291</v>
       </c>
-    </row>
-    <row r="100" spans="1:3">
+      <c r="D99">
+        <v>1.493</v>
+      </c>
+      <c r="E99">
+        <v>0.826</v>
+      </c>
+      <c r="F99">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>45325.3402777778</v>
+        <v>45325.34027777778</v>
       </c>
       <c r="B100">
         <v>2.4</v>
       </c>
-      <c r="C100" s="1">
+      <c r="C100">
         <v>0.291</v>
       </c>
-    </row>
-    <row r="101" spans="1:3">
+      <c r="D100">
+        <v>1.484</v>
+      </c>
+      <c r="E100">
+        <v>0.827</v>
+      </c>
+      <c r="F100">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" s="2">
         <v>45325.34375</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
-      <c r="C101" s="1">
+      <c r="C101">
         <v>0.29</v>
       </c>
-    </row>
-    <row r="102" spans="1:3">
+      <c r="D101">
+        <v>1.482</v>
+      </c>
+      <c r="E101">
+        <v>0.826</v>
+      </c>
+      <c r="F101">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>45325.3472222222</v>
+        <v>45325.34722222222</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
-      <c r="C102" s="1">
+      <c r="C102">
         <v>0.29</v>
       </c>
-    </row>
-    <row r="103" spans="1:3">
+      <c r="D102">
+        <v>1.482</v>
+      </c>
+      <c r="E102">
+        <v>0.825</v>
+      </c>
+      <c r="F102">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>45325.3506944444</v>
+        <v>45325.35069444445</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
-      <c r="C103" s="1">
+      <c r="C103">
         <v>0.288</v>
       </c>
-    </row>
-    <row r="104" spans="1:3">
+      <c r="D103">
+        <v>1.484</v>
+      </c>
+      <c r="E103">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="F103">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>45325.3541666667</v>
+        <v>45325.35416666666</v>
       </c>
       <c r="B104">
         <v>0</v>
       </c>
-      <c r="C104" s="1">
+      <c r="C104">
         <v>0.286</v>
       </c>
-    </row>
-    <row r="105" spans="1:3">
+      <c r="D104">
+        <v>1.478</v>
+      </c>
+      <c r="E104">
+        <v>0.821</v>
+      </c>
+      <c r="F104">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>45325.3576388889</v>
+        <v>45325.35763888889</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
-      <c r="C105" s="1">
+      <c r="C105">
         <v>0.282</v>
       </c>
-    </row>
-    <row r="106" spans="1:3">
+      <c r="D105">
+        <v>1.474</v>
+      </c>
+      <c r="E105">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F105">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>45325.3611111111</v>
+        <v>45325.36111111111</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C106">
         <v>0.289</v>
       </c>
-    </row>
-    <row r="107" spans="1:3">
+      <c r="D106">
+        <v>1.472</v>
+      </c>
+      <c r="E106">
+        <v>0.806</v>
+      </c>
+      <c r="F106">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>45325.3645833333</v>
+        <v>45325.36458333334</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
-      <c r="C107" s="1">
+      <c r="C107">
         <v>0.28</v>
       </c>
-    </row>
-    <row r="108" spans="1:3">
+      <c r="D107">
+        <v>1.461</v>
+      </c>
+      <c r="E107">
+        <v>0.803</v>
+      </c>
+      <c r="F107">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>45325.3680555556</v>
+        <v>45325.36805555555</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
-      <c r="C108" s="1">
+      <c r="C108">
         <v>0.281</v>
       </c>
-    </row>
-    <row r="109" spans="1:3">
+      <c r="D108">
+        <v>1.463</v>
+      </c>
+      <c r="E108">
+        <v>0.795</v>
+      </c>
+      <c r="F108">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>45325.3715277778</v>
+        <v>45325.37152777778</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
-      <c r="C109" s="1">
+      <c r="C109">
         <v>0.284</v>
       </c>
-    </row>
-    <row r="110" spans="1:3">
+      <c r="D109">
+        <v>1.456</v>
+      </c>
+      <c r="E109">
+        <v>0.795</v>
+      </c>
+      <c r="F109">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" s="2">
         <v>45325.375</v>
       </c>
       <c r="B110">
         <v>2.4</v>
       </c>
-      <c r="C110" s="1">
+      <c r="C110">
         <v>0.279</v>
       </c>
-    </row>
-    <row r="111" spans="1:3">
+      <c r="D110">
+        <v>1.455</v>
+      </c>
+      <c r="E110">
+        <v>0.794</v>
+      </c>
+      <c r="F110">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>45325.3784722222</v>
+        <v>45325.37847222222</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
-      <c r="C111" s="1">
+      <c r="C111">
         <v>0.28</v>
       </c>
-    </row>
-    <row r="112" spans="1:3">
+      <c r="D111">
+        <v>1.452</v>
+      </c>
+      <c r="E111">
+        <v>0.785</v>
+      </c>
+      <c r="F111">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>45325.3819444444</v>
+        <v>45325.38194444445</v>
       </c>
       <c r="B112">
         <v>2.4</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C112">
         <v>0.279</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
+      <c r="D112">
+        <v>1.451</v>
+      </c>
+      <c r="E112">
+        <v>0.794</v>
+      </c>
+      <c r="F112">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>45325.3854166667</v>
+        <v>45325.38541666666</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
-      <c r="C113" s="1">
+      <c r="C113">
         <v>0.28</v>
       </c>
-    </row>
-    <row r="114" spans="1:3">
+      <c r="D113">
+        <v>1.451</v>
+      </c>
+      <c r="E113">
+        <v>0.784</v>
+      </c>
+      <c r="F113">
+        <v>0.119</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>45325.3888888889</v>
+        <v>45325.38888888889</v>
       </c>
       <c r="B114">
         <v>2.4</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C114">
         <v>0.278</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
+      <c r="D114">
+        <v>1.44</v>
+      </c>
+      <c r="E114">
+        <v>0.783</v>
+      </c>
+      <c r="F114">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>45325.3923611111</v>
+        <v>45325.39236111111</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C115">
         <v>0.28</v>
       </c>
-    </row>
-    <row r="116" spans="1:3">
+      <c r="D115">
+        <v>1.452</v>
+      </c>
+      <c r="E115">
+        <v>0.784</v>
+      </c>
+      <c r="F115">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>45325.3958333333</v>
+        <v>45325.39583333334</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C116">
         <v>0.278</v>
       </c>
-    </row>
-    <row r="117" spans="1:3">
+      <c r="D116">
+        <v>1.451</v>
+      </c>
+      <c r="E116">
+        <v>0.794</v>
+      </c>
+      <c r="F116">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>45325.3993055556</v>
+        <v>45325.39930555555</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
-      <c r="C117" s="1">
+      <c r="C117">
         <v>0.278</v>
       </c>
-    </row>
-    <row r="118" spans="1:3">
+      <c r="D117">
+        <v>1.461</v>
+      </c>
+      <c r="E117">
+        <v>0.793</v>
+      </c>
+      <c r="F117">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>45325.4027777778</v>
+        <v>45325.40277777778</v>
       </c>
       <c r="B118">
         <v>0</v>
       </c>
-      <c r="C118" s="1">
+      <c r="C118">
         <v>0.289</v>
       </c>
-    </row>
-    <row r="119" spans="1:3">
+      <c r="D118">
+        <v>1.462</v>
+      </c>
+      <c r="E118">
+        <v>0.797</v>
+      </c>
+      <c r="F118">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" s="2">
         <v>45325.40625</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
-      <c r="C119" s="1">
+      <c r="C119">
         <v>0.277</v>
       </c>
-    </row>
-    <row r="120" spans="1:3">
+      <c r="D119">
+        <v>1.46</v>
+      </c>
+      <c r="E119">
+        <v>0.802</v>
+      </c>
+      <c r="F119">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>45325.4097222222</v>
+        <v>45325.40972222222</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
-      <c r="C120" s="1">
+      <c r="C120">
         <v>0.276</v>
       </c>
-    </row>
-    <row r="121" spans="1:3">
+      <c r="D120">
+        <v>1.459</v>
+      </c>
+      <c r="E120">
+        <v>0.801</v>
+      </c>
+      <c r="F120">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>45325.4131944444</v>
+        <v>45325.41319444445</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
-      <c r="C121" s="1">
+      <c r="C121">
         <v>0.277</v>
       </c>
-    </row>
-    <row r="122" spans="1:3">
+      <c r="D121">
+        <v>1.459</v>
+      </c>
+      <c r="E121">
+        <v>0.801</v>
+      </c>
+      <c r="F121">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>45325.4166666667</v>
+        <v>45325.41666666666</v>
       </c>
       <c r="B122">
         <v>2.4</v>
       </c>
-      <c r="C122" s="1">
+      <c r="C122">
         <v>0.279</v>
       </c>
-    </row>
-    <row r="123" spans="1:3">
+      <c r="D122">
+        <v>1.461</v>
+      </c>
+      <c r="E122">
+        <v>0.8</v>
+      </c>
+      <c r="F122">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>45325.4201388889</v>
+        <v>45325.42013888889</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
-      <c r="C123" s="1">
+      <c r="C123">
         <v>0.287</v>
       </c>
-    </row>
-    <row r="124" spans="1:3">
+      <c r="D123">
+        <v>1.463</v>
+      </c>
+      <c r="E123">
+        <v>0.795</v>
+      </c>
+      <c r="F123">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>45325.4236111111</v>
+        <v>45325.42361111111</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
-      <c r="C124" s="1">
+      <c r="C124">
         <v>0.281</v>
       </c>
-    </row>
-    <row r="125" spans="1:3">
+      <c r="D124">
+        <v>1.454</v>
+      </c>
+      <c r="E124">
+        <v>0.797</v>
+      </c>
+      <c r="F124">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>45325.4270833333</v>
+        <v>45325.42708333334</v>
       </c>
       <c r="B125">
         <v>0</v>
       </c>
-      <c r="C125" s="1">
+      <c r="C125">
         <v>0.279</v>
       </c>
-    </row>
-    <row r="126" spans="1:3">
+      <c r="D125">
+        <v>1.455</v>
+      </c>
+      <c r="E125">
+        <v>0.788</v>
+      </c>
+      <c r="F125">
+        <v>0.119</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>45325.4305555556</v>
+        <v>45325.43055555555</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
-      <c r="C126" s="1">
+      <c r="C126">
         <v>0.281</v>
       </c>
-    </row>
-    <row r="127" spans="1:3">
+      <c r="D126">
+        <v>1.453</v>
+      </c>
+      <c r="E126">
+        <v>0.789</v>
+      </c>
+      <c r="F126">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>45325.4340277778</v>
+        <v>45325.43402777778</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
-      <c r="C127" s="1">
+      <c r="C127">
         <v>0.28</v>
       </c>
-    </row>
-    <row r="128" spans="1:3">
+      <c r="D127">
+        <v>1.452</v>
+      </c>
+      <c r="E127">
+        <v>0.785</v>
+      </c>
+      <c r="F127">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" s="2">
         <v>45325.4375</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
-      <c r="C128" s="1">
+      <c r="C128">
         <v>0.281</v>
       </c>
-    </row>
-    <row r="129" spans="1:3">
+      <c r="D128">
+        <v>1.442</v>
+      </c>
+      <c r="E128">
+        <v>0.784</v>
+      </c>
+      <c r="F128">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>45325.4409722222</v>
+        <v>45325.44097222222</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C129">
         <v>0.271</v>
       </c>
-    </row>
-    <row r="130" spans="1:3">
+      <c r="D129">
+        <v>1.443</v>
+      </c>
+      <c r="E129">
+        <v>0.783</v>
+      </c>
+      <c r="F129">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>45325.4444444444</v>
+        <v>45325.44444444445</v>
       </c>
       <c r="B130">
         <v>0</v>
       </c>
-      <c r="C130" s="1">
+      <c r="C130">
         <v>0.275</v>
       </c>
-    </row>
-    <row r="131" spans="1:3">
+      <c r="D130">
+        <v>1.442</v>
+      </c>
+      <c r="E130">
+        <v>0.776</v>
+      </c>
+      <c r="F130">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>45325.4479166667</v>
+        <v>45325.44791666666</v>
       </c>
       <c r="B131">
         <v>0</v>
       </c>
-      <c r="C131" s="1">
+      <c r="C131">
         <v>0.275</v>
       </c>
-    </row>
-    <row r="132" spans="1:3">
+      <c r="D131">
+        <v>1.436</v>
+      </c>
+      <c r="E131">
+        <v>0.779</v>
+      </c>
+      <c r="F131">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>45325.4513888889</v>
+        <v>45325.45138888889</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
-      <c r="C132" s="1">
+      <c r="C132">
         <v>0.276</v>
       </c>
-    </row>
-    <row r="133" spans="1:3">
+      <c r="D132">
+        <v>1.435</v>
+      </c>
+      <c r="E132">
+        <v>0.771</v>
+      </c>
+      <c r="F132">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>45325.4548611111</v>
+        <v>45325.45486111111</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
-      <c r="C133" s="1">
+      <c r="C133">
         <v>0.275</v>
       </c>
-    </row>
-    <row r="134" spans="1:3">
+      <c r="D133">
+        <v>1.427</v>
+      </c>
+      <c r="E133">
+        <v>0.77</v>
+      </c>
+      <c r="F133">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>45325.4583333333</v>
+        <v>45325.45833333334</v>
       </c>
       <c r="B134">
         <v>0</v>
       </c>
-      <c r="C134" s="1">
+      <c r="C134">
         <v>0.273</v>
       </c>
-    </row>
-    <row r="135" spans="1:3">
+      <c r="D134">
+        <v>1.435</v>
+      </c>
+      <c r="E134">
+        <v>0.768</v>
+      </c>
+      <c r="F134">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>45325.4618055556</v>
+        <v>45325.46180555555</v>
       </c>
       <c r="B135">
         <v>0</v>
       </c>
-      <c r="C135" s="1">
+      <c r="C135">
         <v>0.273</v>
       </c>
-    </row>
-    <row r="136" spans="1:3">
+      <c r="D135">
+        <v>1.425</v>
+      </c>
+      <c r="E135">
+        <v>0.768</v>
+      </c>
+      <c r="F135">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>45325.4652777778</v>
+        <v>45325.46527777778</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
-      <c r="C136" s="1">
+      <c r="C136">
         <v>0.275</v>
       </c>
-    </row>
-    <row r="137" spans="1:3">
+      <c r="D136">
+        <v>1.426</v>
+      </c>
+      <c r="E136">
+        <v>0.768</v>
+      </c>
+      <c r="F136">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" s="2">
         <v>45325.46875</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
-      <c r="C137" s="1">
+      <c r="C137">
         <v>0.273</v>
       </c>
-    </row>
-    <row r="138" spans="1:3">
+      <c r="D137">
+        <v>1.425</v>
+      </c>
+      <c r="E137">
+        <v>0.768</v>
+      </c>
+      <c r="F137">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>45325.4722222222</v>
+        <v>45325.47222222222</v>
       </c>
       <c r="B138">
         <v>0</v>
       </c>
-      <c r="C138" s="1">
+      <c r="C138">
         <v>0.275</v>
       </c>
-    </row>
-    <row r="139" spans="1:3">
+      <c r="D138">
+        <v>1.426</v>
+      </c>
+      <c r="E138">
+        <v>0.758</v>
+      </c>
+      <c r="F138">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>45325.4756944444</v>
+        <v>45325.47569444445</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
-      <c r="C139" s="1">
+      <c r="C139">
         <v>0.269</v>
       </c>
-    </row>
-    <row r="140" spans="1:3">
+      <c r="D139">
+        <v>1.418</v>
+      </c>
+      <c r="E139">
+        <v>0.76</v>
+      </c>
+      <c r="F139">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>45325.4791666667</v>
+        <v>45325.47916666666</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
-      <c r="C140" s="1">
+      <c r="C140">
         <v>0.273</v>
       </c>
-    </row>
-    <row r="141" spans="1:3">
+      <c r="D140">
+        <v>1.427</v>
+      </c>
+      <c r="E140">
+        <v>0.76</v>
+      </c>
+      <c r="F140">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>45325.4826388889</v>
+        <v>45325.48263888889</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
-      <c r="C141" s="1">
+      <c r="C141">
         <v>0.275</v>
       </c>
-    </row>
-    <row r="142" spans="1:3">
+      <c r="D141">
+        <v>1.417</v>
+      </c>
+      <c r="E141">
+        <v>0.76</v>
+      </c>
+      <c r="F141">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>45325.4861111111</v>
+        <v>45325.48611111111</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
-      <c r="C142" s="1">
+      <c r="C142">
         <v>0.266</v>
       </c>
-    </row>
-    <row r="143" spans="1:3">
+      <c r="D142">
+        <v>1.418</v>
+      </c>
+      <c r="E142">
+        <v>0.761</v>
+      </c>
+      <c r="F142">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>45325.4895833333</v>
+        <v>45325.48958333334</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
-      <c r="C143" s="1">
+      <c r="C143">
         <v>0.276</v>
       </c>
-    </row>
-    <row r="144" spans="1:3">
+      <c r="D143">
+        <v>1.417</v>
+      </c>
+      <c r="E143">
+        <v>0.75</v>
+      </c>
+      <c r="F143">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>45325.4930555556</v>
+        <v>45325.49305555555</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
-      <c r="C144" s="1">
+      <c r="C144">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="145" spans="1:3">
+      <c r="D144">
+        <v>1.408</v>
+      </c>
+      <c r="E144">
+        <v>0.751</v>
+      </c>
+      <c r="F144">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>45325.4965277778</v>
+        <v>45325.49652777778</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
-      <c r="C145" s="1">
+      <c r="C145">
         <v>0.265</v>
       </c>
-    </row>
-    <row r="146" spans="1:3">
+      <c r="D145">
+        <v>1.412</v>
+      </c>
+      <c r="E145">
+        <v>0.749</v>
+      </c>
+      <c r="F145">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" s="2">
         <v>45325.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
-      <c r="C146" s="1">
+      <c r="C146">
         <v>0.272</v>
       </c>
-    </row>
-    <row r="147" spans="1:3">
+      <c r="D146">
+        <v>1.413</v>
+      </c>
+      <c r="E146">
+        <v>0.756</v>
+      </c>
+      <c r="F146">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>45325.5034722222</v>
+        <v>45325.50347222222</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
-      <c r="C147" s="1">
+      <c r="C147">
         <v>0.274</v>
       </c>
-    </row>
-    <row r="148" spans="1:3">
+      <c r="D147">
+        <v>1.406</v>
+      </c>
+      <c r="E147">
+        <v>0.748</v>
+      </c>
+      <c r="F147">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>45325.5069444444</v>
+        <v>45325.50694444445</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
-      <c r="C148" s="1">
+      <c r="C148">
         <v>0.265</v>
       </c>
-    </row>
-    <row r="149" spans="1:3">
+      <c r="D148">
+        <v>1.406</v>
+      </c>
+      <c r="E148">
+        <v>0.749</v>
+      </c>
+      <c r="F148">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>45325.5104166667</v>
+        <v>45325.51041666666</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
-      <c r="C149" s="1">
+      <c r="C149">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="150" spans="1:3">
+      <c r="D149">
+        <v>1.42</v>
+      </c>
+      <c r="E149">
+        <v>0.761</v>
+      </c>
+      <c r="F149">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>45325.5138888889</v>
+        <v>45325.51388888889</v>
       </c>
       <c r="B150">
         <v>0</v>
       </c>
-      <c r="C150" s="1">
+      <c r="C150">
         <v>0.269</v>
       </c>
-    </row>
-    <row r="151" spans="1:3">
+      <c r="D150">
+        <v>1.441</v>
+      </c>
+      <c r="E150">
+        <v>0.784</v>
+      </c>
+      <c r="F150">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>45325.5173611111</v>
+        <v>45325.51736111111</v>
       </c>
       <c r="B151">
         <v>0</v>
       </c>
-      <c r="C151" s="1">
+      <c r="C151">
         <v>0.271</v>
       </c>
-    </row>
-    <row r="152" spans="1:3">
+      <c r="D151">
+        <v>1.444</v>
+      </c>
+      <c r="E151">
+        <v>0.779</v>
+      </c>
+      <c r="F151">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>45325.5208333333</v>
+        <v>45325.52083333334</v>
       </c>
       <c r="B152">
         <v>0</v>
       </c>
-      <c r="C152" s="1">
+      <c r="C152">
         <v>0.264</v>
       </c>
-    </row>
-    <row r="153" spans="1:3">
+      <c r="D152">
+        <v>1.44</v>
+      </c>
+      <c r="E152">
+        <v>0.78</v>
+      </c>
+      <c r="F152">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>45325.5243055556</v>
+        <v>45325.52430555555</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
-      <c r="C153" s="1">
+      <c r="C153">
         <v>0.267</v>
       </c>
-    </row>
-    <row r="154" spans="1:3">
+      <c r="D153">
+        <v>1.44</v>
+      </c>
+      <c r="E153">
+        <v>0.782</v>
+      </c>
+      <c r="F153">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>45325.5277777778</v>
+        <v>45325.52777777778</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
-      <c r="C154" s="1">
+      <c r="C154">
         <v>0.268</v>
       </c>
-    </row>
-    <row r="155" spans="1:3">
+      <c r="D154">
+        <v>1.44</v>
+      </c>
+      <c r="E154">
+        <v>0.783</v>
+      </c>
+      <c r="F154">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" s="2">
         <v>45325.53125</v>
       </c>
       <c r="B155">
         <v>0</v>
       </c>
-      <c r="C155" s="1">
+      <c r="C155">
         <v>0.269</v>
       </c>
-    </row>
-    <row r="156" spans="1:3">
+      <c r="D155">
+        <v>1.441</v>
+      </c>
+      <c r="E155">
+        <v>0.777</v>
+      </c>
+      <c r="F155">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>45325.5347222222</v>
+        <v>45325.53472222222</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
-      <c r="C156" s="1">
+      <c r="C156">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="157" spans="1:3">
+      <c r="D156">
+        <v>1.443</v>
+      </c>
+      <c r="E156">
+        <v>0.775</v>
+      </c>
+      <c r="F156">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>45325.5381944444</v>
+        <v>45325.53819444445</v>
       </c>
       <c r="B157">
         <v>0</v>
       </c>
-      <c r="C157" s="1">
+      <c r="C157">
         <v>0.272</v>
       </c>
-    </row>
-    <row r="158" spans="1:3">
+      <c r="D157">
+        <v>1.446</v>
+      </c>
+      <c r="E157">
+        <v>0.787</v>
+      </c>
+      <c r="F157">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>45325.5416666667</v>
+        <v>45325.54166666666</v>
       </c>
       <c r="B158">
         <v>0</v>
       </c>
-      <c r="C158" s="1">
+      <c r="C158">
         <v>0.264</v>
       </c>
-    </row>
-    <row r="159" spans="1:3">
+      <c r="D158">
+        <v>1.436</v>
+      </c>
+      <c r="E158">
+        <v>0.779</v>
+      </c>
+      <c r="F158">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>45325.5451388889</v>
+        <v>45325.54513888889</v>
       </c>
       <c r="B159">
         <v>0</v>
       </c>
-      <c r="C159" s="1">
+      <c r="C159">
         <v>0.263</v>
       </c>
-    </row>
-    <row r="160" spans="1:3">
+      <c r="D159">
+        <v>1.435</v>
+      </c>
+      <c r="E159">
+        <v>0.778</v>
+      </c>
+      <c r="F159">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>45325.5486111111</v>
+        <v>45325.54861111111</v>
       </c>
       <c r="B160">
         <v>0</v>
       </c>
-      <c r="C160" s="1">
+      <c r="C160">
         <v>0.263</v>
       </c>
-    </row>
-    <row r="161" spans="1:3">
+      <c r="D160">
+        <v>1.435</v>
+      </c>
+      <c r="E160">
+        <v>0.778</v>
+      </c>
+      <c r="F160">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>45325.5520833333</v>
+        <v>45325.55208333334</v>
       </c>
       <c r="B161">
         <v>0</v>
       </c>
-      <c r="C161" s="1">
+      <c r="C161">
         <v>0.264</v>
       </c>
-    </row>
-    <row r="162" spans="1:3">
+      <c r="D161">
+        <v>1.446</v>
+      </c>
+      <c r="E161">
+        <v>0.779</v>
+      </c>
+      <c r="F161">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>45325.5555555556</v>
+        <v>45325.55555555555</v>
       </c>
       <c r="B162">
         <v>0</v>
       </c>
-      <c r="C162" s="1">
+      <c r="C162">
         <v>0.265</v>
       </c>
-    </row>
-    <row r="163" spans="1:3">
+      <c r="D162">
+        <v>1.437</v>
+      </c>
+      <c r="E162">
+        <v>0.78</v>
+      </c>
+      <c r="F162">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>45325.5590277778</v>
+        <v>45325.55902777778</v>
       </c>
       <c r="B163">
         <v>0</v>
       </c>
-      <c r="C163" s="1">
+      <c r="C163">
         <v>0.266</v>
       </c>
-    </row>
-    <row r="164" spans="1:3">
+      <c r="D163">
+        <v>1.438</v>
+      </c>
+      <c r="E163">
+        <v>0.781</v>
+      </c>
+      <c r="F163">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164" s="2">
         <v>45325.5625</v>
       </c>
       <c r="B164">
         <v>0</v>
       </c>
-      <c r="C164" s="1">
+      <c r="C164">
         <v>0.268</v>
       </c>
-    </row>
-    <row r="165" spans="1:3">
+      <c r="D164">
+        <v>1.441</v>
+      </c>
+      <c r="E164">
+        <v>0.783</v>
+      </c>
+      <c r="F164">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>45325.5659722222</v>
+        <v>45325.56597222222</v>
       </c>
       <c r="B165">
         <v>0</v>
       </c>
-      <c r="C165" s="1">
+      <c r="C165">
         <v>0.267</v>
       </c>
-    </row>
-    <row r="166" spans="1:3">
+      <c r="D165">
+        <v>1.438</v>
+      </c>
+      <c r="E165">
+        <v>0.782</v>
+      </c>
+      <c r="F165">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>45325.5694444444</v>
+        <v>45325.56944444445</v>
       </c>
       <c r="B166">
         <v>0</v>
       </c>
-      <c r="C166" s="1">
+      <c r="C166">
         <v>0.268</v>
       </c>
-    </row>
-    <row r="167" spans="1:3">
+      <c r="D166">
+        <v>1.44</v>
+      </c>
+      <c r="E166">
+        <v>0.782</v>
+      </c>
+      <c r="F166">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>45325.5729166667</v>
+        <v>45325.57291666666</v>
       </c>
       <c r="B167">
         <v>0</v>
       </c>
-      <c r="C167" s="1">
+      <c r="C167">
         <v>0.268</v>
       </c>
-    </row>
-    <row r="168" spans="1:3">
+      <c r="D167">
+        <v>1.44</v>
+      </c>
+      <c r="E167">
+        <v>0.783</v>
+      </c>
+      <c r="F167">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>45325.5763888889</v>
+        <v>45325.57638888889</v>
       </c>
       <c r="B168">
         <v>0</v>
       </c>
-      <c r="C168" s="1">
+      <c r="C168">
         <v>0.268</v>
       </c>
-    </row>
-    <row r="169" spans="1:3">
+      <c r="D168">
+        <v>1.44</v>
+      </c>
+      <c r="E168">
+        <v>0.783</v>
+      </c>
+      <c r="F168">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>45325.5798611111</v>
+        <v>45325.57986111111</v>
       </c>
       <c r="B169">
         <v>0</v>
       </c>
-      <c r="C169" s="1">
+      <c r="C169">
         <v>0.268</v>
       </c>
-    </row>
-    <row r="170" spans="1:3">
+      <c r="D169">
+        <v>1.44</v>
+      </c>
+      <c r="E169">
+        <v>0.783</v>
+      </c>
+      <c r="F169">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>45325.5833333333</v>
+        <v>45325.58333333334</v>
       </c>
       <c r="B170">
         <v>0</v>
       </c>
-      <c r="C170" s="1">
+      <c r="C170">
         <v>0.269</v>
       </c>
-    </row>
-    <row r="171" spans="1:3">
+      <c r="D170">
+        <v>1.44</v>
+      </c>
+      <c r="E170">
+        <v>0.783</v>
+      </c>
+      <c r="F170">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>45325.5868055556</v>
+        <v>45325.58680555555</v>
       </c>
       <c r="B171">
         <v>0</v>
       </c>
-      <c r="C171" s="1">
+      <c r="C171">
         <v>0.269</v>
       </c>
-    </row>
-    <row r="172" spans="1:3">
+      <c r="D171">
+        <v>1.441</v>
+      </c>
+      <c r="E171">
+        <v>0.784</v>
+      </c>
+      <c r="F171">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>45325.5902777778</v>
+        <v>45325.59027777778</v>
       </c>
       <c r="B172">
         <v>0</v>
       </c>
-      <c r="C172" s="1">
+      <c r="C172">
         <v>0.269</v>
       </c>
-    </row>
-    <row r="173" spans="1:3">
+      <c r="D172">
+        <v>1.442</v>
+      </c>
+      <c r="E172">
+        <v>0.785</v>
+      </c>
+      <c r="F172">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
       <c r="A173" s="2">
         <v>45325.59375</v>
       </c>
       <c r="B173">
         <v>0</v>
       </c>
-      <c r="C173" s="1">
+      <c r="C173">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="174" spans="1:3">
+      <c r="D173">
+        <v>1.442</v>
+      </c>
+      <c r="E173">
+        <v>0.778</v>
+      </c>
+      <c r="F173">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>45325.5972222222</v>
+        <v>45325.59722222222</v>
       </c>
       <c r="B174">
         <v>0</v>
       </c>
-      <c r="C174" s="1">
+      <c r="C174">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="175" spans="1:3">
+      <c r="D174">
+        <v>1.442</v>
+      </c>
+      <c r="E174">
+        <v>0.775</v>
+      </c>
+      <c r="F174">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>45325.6006944444</v>
+        <v>45325.60069444445</v>
       </c>
       <c r="B175">
         <v>0</v>
       </c>
-      <c r="C175" s="1">
+      <c r="C175">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="176" spans="1:3">
+      <c r="D175">
+        <v>1.443</v>
+      </c>
+      <c r="E175">
+        <v>0.778</v>
+      </c>
+      <c r="F175">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>45325.6041666667</v>
+        <v>45325.60416666666</v>
       </c>
       <c r="B176">
         <v>0</v>
       </c>
-      <c r="C176" s="1">
+      <c r="C176">
         <v>0.268</v>
       </c>
-    </row>
-    <row r="177" spans="1:3">
+      <c r="D176">
+        <v>1.44</v>
+      </c>
+      <c r="E176">
+        <v>0.776</v>
+      </c>
+      <c r="F176">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>45325.6076388889</v>
+        <v>45325.60763888889</v>
       </c>
       <c r="B177">
         <v>0</v>
       </c>
-      <c r="C177" s="1">
+      <c r="C177">
         <v>0.265</v>
       </c>
-    </row>
-    <row r="178" spans="1:3">
+      <c r="D177">
+        <v>1.434</v>
+      </c>
+      <c r="E177">
+        <v>0.777</v>
+      </c>
+      <c r="F177">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>45325.6111111111</v>
+        <v>45325.61111111111</v>
       </c>
       <c r="B178">
         <v>0</v>
       </c>
-      <c r="C178" s="1">
+      <c r="C178">
         <v>0.268</v>
       </c>
-    </row>
-    <row r="179" spans="1:3">
+      <c r="D178">
+        <v>1.436</v>
+      </c>
+      <c r="E178">
+        <v>0.776</v>
+      </c>
+      <c r="F178">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>45325.6145833333</v>
+        <v>45325.61458333334</v>
       </c>
       <c r="B179">
         <v>0</v>
       </c>
-      <c r="C179" s="1">
+      <c r="C179">
         <v>0.261</v>
       </c>
-    </row>
-    <row r="180" spans="1:3">
+      <c r="D179">
+        <v>1.436</v>
+      </c>
+      <c r="E179">
+        <v>0.776</v>
+      </c>
+      <c r="F179">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>45325.6180555556</v>
+        <v>45325.61805555555</v>
       </c>
       <c r="B180">
         <v>0</v>
       </c>
-      <c r="C180" s="1">
+      <c r="C180">
         <v>0.263</v>
       </c>
-    </row>
-    <row r="181" spans="1:3">
+      <c r="D180">
+        <v>1.432</v>
+      </c>
+      <c r="E180">
+        <v>0.775</v>
+      </c>
+      <c r="F180">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>45325.6215277778</v>
+        <v>45325.62152777778</v>
       </c>
       <c r="B181">
         <v>0</v>
       </c>
-      <c r="C181" s="1">
+      <c r="C181">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="182" spans="1:3">
+      <c r="D181">
+        <v>1.432</v>
+      </c>
+      <c r="E181">
+        <v>0.775</v>
+      </c>
+      <c r="F181">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
       <c r="A182" s="2">
         <v>45325.625</v>
       </c>
       <c r="B182">
         <v>0</v>
       </c>
-      <c r="C182" s="1">
+      <c r="C182">
         <v>0.266</v>
       </c>
-    </row>
-    <row r="183" spans="1:3">
+      <c r="D182">
+        <v>1.431</v>
+      </c>
+      <c r="E182">
+        <v>0.774</v>
+      </c>
+      <c r="F182">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>45325.6284722222</v>
+        <v>45325.62847222222</v>
       </c>
       <c r="B183">
         <v>0</v>
       </c>
-      <c r="C183" s="1">
+      <c r="C183">
         <v>0.266</v>
       </c>
-    </row>
-    <row r="184" spans="1:3">
+      <c r="D183">
+        <v>1.441</v>
+      </c>
+      <c r="E183">
+        <v>0.775</v>
+      </c>
+      <c r="F183">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>45325.6319444444</v>
+        <v>45325.63194444445</v>
       </c>
       <c r="B184">
         <v>0</v>
       </c>
-      <c r="C184" s="1">
+      <c r="C184">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="185" spans="1:3">
+      <c r="D184">
+        <v>1.432</v>
+      </c>
+      <c r="E184">
+        <v>0.775</v>
+      </c>
+      <c r="F184">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>45325.6354166667</v>
+        <v>45325.63541666666</v>
       </c>
       <c r="B185">
         <v>0</v>
       </c>
-      <c r="C185" s="1">
+      <c r="C185">
         <v>0.263</v>
       </c>
-    </row>
-    <row r="186" spans="1:3">
+      <c r="D185">
+        <v>1.431</v>
+      </c>
+      <c r="E185">
+        <v>0.775</v>
+      </c>
+      <c r="F185">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>45325.6388888889</v>
+        <v>45325.63888888889</v>
       </c>
       <c r="B186">
         <v>0</v>
       </c>
-      <c r="C186" s="1">
+      <c r="C186">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="187" spans="1:3">
+      <c r="D186">
+        <v>1.438</v>
+      </c>
+      <c r="E186">
+        <v>0.772</v>
+      </c>
+      <c r="F186">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>45325.6423611111</v>
+        <v>45325.64236111111</v>
       </c>
       <c r="B187">
         <v>0</v>
       </c>
-      <c r="C187" s="1">
+      <c r="C187">
         <v>0.266</v>
       </c>
-    </row>
-    <row r="188" spans="1:3">
+      <c r="D187">
+        <v>1.437</v>
+      </c>
+      <c r="E187">
+        <v>0.78</v>
+      </c>
+      <c r="F187">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>45325.6458333333</v>
+        <v>45325.64583333334</v>
       </c>
       <c r="B188">
         <v>0</v>
       </c>
-      <c r="C188" s="1">
+      <c r="C188">
         <v>0.264</v>
       </c>
-    </row>
-    <row r="189" spans="1:3">
+      <c r="D188">
+        <v>1.436</v>
+      </c>
+      <c r="E188">
+        <v>0.776</v>
+      </c>
+      <c r="F188">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>45325.6493055556</v>
+        <v>45325.64930555555</v>
       </c>
       <c r="B189">
         <v>0</v>
       </c>
-      <c r="C189" s="1">
+      <c r="C189">
         <v>0.262</v>
       </c>
-    </row>
-    <row r="190" spans="1:3">
+      <c r="D189">
+        <v>1.438</v>
+      </c>
+      <c r="E189">
+        <v>0.775</v>
+      </c>
+      <c r="F189">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>45325.6527777778</v>
+        <v>45325.65277777778</v>
       </c>
       <c r="B190">
         <v>0</v>
       </c>
-      <c r="C190" s="1">
+      <c r="C190">
         <v>0.255</v>
       </c>
-    </row>
-    <row r="191" spans="1:3">
+      <c r="D190">
+        <v>1.436</v>
+      </c>
+      <c r="E190">
+        <v>0.776</v>
+      </c>
+      <c r="F190">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
       <c r="A191" s="2">
         <v>45325.65625</v>
       </c>
       <c r="B191">
         <v>0</v>
       </c>
-      <c r="C191" s="1">
+      <c r="C191">
         <v>0.262</v>
       </c>
-    </row>
-    <row r="192" spans="1:3">
+      <c r="D191">
+        <v>1.437</v>
+      </c>
+      <c r="E191">
+        <v>0.77</v>
+      </c>
+      <c r="F191">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>45325.6597222222</v>
+        <v>45325.65972222222</v>
       </c>
       <c r="B192">
         <v>0</v>
       </c>
-      <c r="C192" s="1">
+      <c r="C192">
         <v>0.267</v>
       </c>
-    </row>
-    <row r="193" spans="1:3">
+      <c r="D192">
+        <v>1.428</v>
+      </c>
+      <c r="E192">
+        <v>0.771</v>
+      </c>
+      <c r="F192">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>45325.6631944444</v>
+        <v>45325.66319444445</v>
       </c>
       <c r="B193">
         <v>0</v>
       </c>
-      <c r="C193" s="1">
+      <c r="C193">
         <v>0.257</v>
       </c>
-    </row>
-    <row r="194" spans="1:3">
+      <c r="D193">
+        <v>1.429</v>
+      </c>
+      <c r="E193">
+        <v>0.772</v>
+      </c>
+      <c r="F193">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
       <c r="A194" s="2">
-        <v>45325.6666666667</v>
+        <v>45325.66666666666</v>
       </c>
       <c r="B194">
         <v>0</v>
       </c>
-      <c r="C194" s="1">
+      <c r="C194">
         <v>0.253</v>
       </c>
-    </row>
-    <row r="195" spans="1:3">
+      <c r="D194">
+        <v>1.424</v>
+      </c>
+      <c r="E194">
+        <v>0.768</v>
+      </c>
+      <c r="F194">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
       <c r="A195" s="2">
-        <v>45325.6701388889</v>
+        <v>45325.67013888889</v>
       </c>
       <c r="B195">
         <v>0</v>
       </c>
-      <c r="C195" s="1">
+      <c r="C195">
         <v>0.261</v>
       </c>
-    </row>
-    <row r="196" spans="1:3">
+      <c r="D195">
+        <v>1.423</v>
+      </c>
+      <c r="E195">
+        <v>0.766</v>
+      </c>
+      <c r="F195">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
       <c r="A196" s="2">
-        <v>45325.6736111111</v>
+        <v>45325.67361111111</v>
       </c>
       <c r="B196">
         <v>0</v>
       </c>
-      <c r="C196" s="1">
+      <c r="C196">
         <v>0.261</v>
       </c>
-    </row>
-    <row r="197" spans="1:3">
+      <c r="D196">
+        <v>1.423</v>
+      </c>
+      <c r="E196">
+        <v>0.766</v>
+      </c>
+      <c r="F196">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
       <c r="A197" s="2">
-        <v>45325.6770833333</v>
+        <v>45325.67708333334</v>
       </c>
       <c r="B197">
         <v>0</v>
       </c>
-      <c r="C197" s="1">
+      <c r="C197">
         <v>0.262</v>
       </c>
-    </row>
-    <row r="198" spans="1:3">
+      <c r="D197">
+        <v>1.424</v>
+      </c>
+      <c r="E197">
+        <v>0.767</v>
+      </c>
+      <c r="F197">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
       <c r="A198" s="2">
-        <v>45325.6805555556</v>
+        <v>45325.68055555555</v>
       </c>
       <c r="B198">
         <v>0</v>
       </c>
-      <c r="C198" s="1">
+      <c r="C198">
         <v>0.259</v>
       </c>
-    </row>
-    <row r="199" spans="1:3">
+      <c r="D198">
+        <v>1.424</v>
+      </c>
+      <c r="E198">
+        <v>0.764</v>
+      </c>
+      <c r="F198">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
       <c r="A199" s="2">
-        <v>45325.6840277778</v>
+        <v>45325.68402777778</v>
       </c>
       <c r="B199">
         <v>0</v>
       </c>
-      <c r="C199" s="1">
+      <c r="C199">
         <v>0.263</v>
       </c>
-    </row>
-    <row r="200" spans="1:3">
+      <c r="D199">
+        <v>1.425</v>
+      </c>
+      <c r="E199">
+        <v>0.758</v>
+      </c>
+      <c r="F199">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
       <c r="A200" s="2">
         <v>45325.6875</v>
       </c>
       <c r="B200">
         <v>0</v>
       </c>
-      <c r="C200" s="1">
+      <c r="C200">
         <v>0.262</v>
       </c>
-    </row>
-    <row r="201" spans="1:3">
+      <c r="D200">
+        <v>1.424</v>
+      </c>
+      <c r="E200">
+        <v>0.757</v>
+      </c>
+      <c r="F200">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
       <c r="A201" s="2">
-        <v>45325.6909722222</v>
+        <v>45325.69097222222</v>
       </c>
       <c r="B201">
         <v>0</v>
       </c>
-      <c r="C201" s="1">
+      <c r="C201">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="202" spans="1:3">
+      <c r="D201">
+        <v>1.421</v>
+      </c>
+      <c r="E201">
+        <v>0.755</v>
+      </c>
+      <c r="F201">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
       <c r="A202" s="2">
-        <v>45325.6944444444</v>
+        <v>45325.69444444445</v>
       </c>
       <c r="B202">
         <v>0</v>
       </c>
-      <c r="C202" s="1">
+      <c r="C202">
         <v>0.261</v>
       </c>
-    </row>
-    <row r="203" spans="1:3">
+      <c r="D202">
+        <v>1.417</v>
+      </c>
+      <c r="E202">
+        <v>0.756</v>
+      </c>
+      <c r="F202">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
       <c r="A203" s="2">
-        <v>45325.6979166667</v>
+        <v>45325.69791666666</v>
       </c>
       <c r="B203">
         <v>0</v>
       </c>
-      <c r="C203" s="1">
+      <c r="C203">
         <v>0.253</v>
       </c>
-    </row>
-    <row r="204" spans="1:3">
+      <c r="D203">
+        <v>1.416</v>
+      </c>
+      <c r="E203">
+        <v>0.758</v>
+      </c>
+      <c r="F203">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
       <c r="A204" s="2">
-        <v>45325.7013888889</v>
+        <v>45325.70138888889</v>
       </c>
       <c r="B204">
         <v>0</v>
       </c>
-      <c r="C204" s="1">
+      <c r="C204">
         <v>0.254</v>
       </c>
-    </row>
-    <row r="205" spans="1:3">
+      <c r="D204">
+        <v>1.416</v>
+      </c>
+      <c r="E204">
+        <v>0.759</v>
+      </c>
+      <c r="F204">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
       <c r="A205" s="2">
-        <v>45325.7048611111</v>
+        <v>45325.70486111111</v>
       </c>
       <c r="B205">
         <v>0</v>
       </c>
-      <c r="C205" s="1">
+      <c r="C205">
         <v>0.257</v>
       </c>
-    </row>
-    <row r="206" spans="1:3">
+      <c r="D205">
+        <v>1.42</v>
+      </c>
+      <c r="E205">
+        <v>0.758</v>
+      </c>
+      <c r="F205">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
       <c r="A206" s="2">
-        <v>45325.7083333333</v>
+        <v>45325.70833333334</v>
       </c>
       <c r="B206">
         <v>0</v>
       </c>
-      <c r="C206" s="1">
+      <c r="C206">
         <v>0.258</v>
       </c>
-    </row>
-    <row r="207" spans="1:3">
+      <c r="D206">
+        <v>1.419</v>
+      </c>
+      <c r="E206">
+        <v>0.753</v>
+      </c>
+      <c r="F206">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
       <c r="A207" s="2">
-        <v>45325.7118055556</v>
+        <v>45325.71180555555</v>
       </c>
       <c r="B207">
         <v>0</v>
       </c>
-      <c r="C207" s="1">
+      <c r="C207">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="208" spans="1:3">
+      <c r="D207">
+        <v>1.415</v>
+      </c>
+      <c r="E207">
+        <v>0.758</v>
+      </c>
+      <c r="F207">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
       <c r="A208" s="2">
-        <v>45325.7152777778</v>
+        <v>45325.71527777778</v>
       </c>
       <c r="B208">
         <v>0</v>
       </c>
-      <c r="C208" s="1">
+      <c r="C208">
         <v>0.259</v>
       </c>
-    </row>
-    <row r="209" spans="1:3">
+      <c r="D208">
+        <v>1.414</v>
+      </c>
+      <c r="E208">
+        <v>0.757</v>
+      </c>
+      <c r="F208">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
       <c r="A209" s="2">
         <v>45325.71875</v>
       </c>
       <c r="B209">
         <v>0</v>
       </c>
-      <c r="C209" s="1">
+      <c r="C209">
         <v>0.258</v>
       </c>
-    </row>
-    <row r="210" spans="1:3">
+      <c r="D209">
+        <v>1.41</v>
+      </c>
+      <c r="E209">
+        <v>0.753</v>
+      </c>
+      <c r="F209">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
       <c r="A210" s="2">
-        <v>45325.7222222222</v>
+        <v>45325.72222222222</v>
       </c>
       <c r="B210">
         <v>0</v>
       </c>
-      <c r="C210" s="1">
+      <c r="C210">
         <v>0.251</v>
       </c>
-    </row>
-    <row r="211" spans="1:3">
+      <c r="D210">
+        <v>1.418</v>
+      </c>
+      <c r="E210">
+        <v>0.751</v>
+      </c>
+      <c r="F210">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
       <c r="A211" s="2">
-        <v>45325.7256944444</v>
+        <v>45325.72569444445</v>
       </c>
       <c r="B211">
         <v>0</v>
       </c>
-      <c r="C211" s="1">
+      <c r="C211">
         <v>0.253</v>
       </c>
-    </row>
-    <row r="212" spans="1:3">
+      <c r="D211">
+        <v>1.415</v>
+      </c>
+      <c r="E211">
+        <v>0.758</v>
+      </c>
+      <c r="F211">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
       <c r="A212" s="2">
-        <v>45325.7291666667</v>
+        <v>45325.72916666666</v>
       </c>
       <c r="B212">
         <v>0</v>
       </c>
-      <c r="C212" s="1">
+      <c r="C212">
         <v>0.259</v>
       </c>
-    </row>
-    <row r="213" spans="1:3">
+      <c r="D212">
+        <v>1.416</v>
+      </c>
+      <c r="E212">
+        <v>0.75</v>
+      </c>
+      <c r="F212">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
       <c r="A213" s="2">
-        <v>45325.7326388889</v>
+        <v>45325.73263888889</v>
       </c>
       <c r="B213">
         <v>0</v>
       </c>
-      <c r="C213" s="1">
+      <c r="C213">
         <v>0.252</v>
       </c>
-    </row>
-    <row r="214" spans="1:3">
+      <c r="D213">
+        <v>1.414</v>
+      </c>
+      <c r="E213">
+        <v>0.757</v>
+      </c>
+      <c r="F213">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
       <c r="A214" s="2">
-        <v>45325.7361111111</v>
+        <v>45325.73611111111</v>
       </c>
       <c r="B214">
         <v>0</v>
       </c>
-      <c r="C214" s="1">
+      <c r="C214">
         <v>0.244</v>
       </c>
-    </row>
-    <row r="215" spans="1:3">
+      <c r="D214">
+        <v>1.417</v>
+      </c>
+      <c r="E214">
+        <v>0.759</v>
+      </c>
+      <c r="F214">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
       <c r="A215" s="2">
-        <v>45325.7395833333</v>
+        <v>45325.73958333334</v>
       </c>
       <c r="B215">
         <v>0</v>
       </c>
-      <c r="C215" s="1">
+      <c r="C215">
         <v>0.253</v>
       </c>
-    </row>
-    <row r="216" spans="1:3">
+      <c r="D215">
+        <v>1.408</v>
+      </c>
+      <c r="E215">
+        <v>0.751</v>
+      </c>
+      <c r="F215">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
       <c r="A216" s="2">
-        <v>45325.7430555556</v>
+        <v>45325.74305555555</v>
       </c>
       <c r="B216">
         <v>0</v>
       </c>
-      <c r="C216" s="1">
+      <c r="C216">
         <v>0.258</v>
       </c>
-    </row>
-    <row r="217" spans="1:3">
+      <c r="D216">
+        <v>1.409</v>
+      </c>
+      <c r="E216">
+        <v>0.752</v>
+      </c>
+      <c r="F216">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
       <c r="A217" s="2">
-        <v>45325.7465277778</v>
+        <v>45325.74652777778</v>
       </c>
       <c r="B217">
         <v>0</v>
       </c>
-      <c r="C217" s="1">
+      <c r="C217">
         <v>0.256</v>
       </c>
-    </row>
-    <row r="218" spans="1:3">
+      <c r="D217">
+        <v>1.408</v>
+      </c>
+      <c r="E217">
+        <v>0.751</v>
+      </c>
+      <c r="F217">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
       <c r="A218" s="2">
         <v>45325.75</v>
       </c>
       <c r="B218">
         <v>0</v>
       </c>
-      <c r="C218" s="1">
+      <c r="C218">
         <v>0.251</v>
       </c>
-    </row>
-    <row r="219" spans="1:3">
+      <c r="D218">
+        <v>1.409</v>
+      </c>
+      <c r="E218">
+        <v>0.752</v>
+      </c>
+      <c r="F218">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
       <c r="A219" s="2">
-        <v>45325.7534722222</v>
+        <v>45325.75347222222</v>
       </c>
       <c r="B219">
         <v>0</v>
       </c>
-      <c r="C219" s="1">
+      <c r="C219">
         <v>0.247</v>
       </c>
-    </row>
-    <row r="220" spans="1:3">
+      <c r="D219">
+        <v>1.408</v>
+      </c>
+      <c r="E219">
+        <v>0.751</v>
+      </c>
+      <c r="F219">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
       <c r="A220" s="2">
-        <v>45325.7569444444</v>
+        <v>45325.75694444445</v>
       </c>
       <c r="B220">
         <v>0</v>
       </c>
-      <c r="C220" s="1">
+      <c r="C220">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="221" spans="1:3">
+      <c r="D220">
+        <v>1.408</v>
+      </c>
+      <c r="E220">
+        <v>0.752</v>
+      </c>
+      <c r="F220">
+        <v>0.103</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
       <c r="A221" s="2">
-        <v>45325.7604166667</v>
+        <v>45325.76041666666</v>
       </c>
       <c r="B221">
         <v>0</v>
       </c>
-      <c r="C221" s="1">
+      <c r="C221">
         <v>0.252</v>
       </c>
-    </row>
-    <row r="222" spans="1:3">
+      <c r="D221">
+        <v>1.406</v>
+      </c>
+      <c r="E221">
+        <v>0.749</v>
+      </c>
+      <c r="F221">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
       <c r="A222" s="2">
-        <v>45325.7638888889</v>
+        <v>45325.76388888889</v>
       </c>
       <c r="B222">
         <v>0</v>
       </c>
-      <c r="C222" s="1">
+      <c r="C222">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="223" spans="1:3">
+      <c r="D222">
+        <v>1.408</v>
+      </c>
+      <c r="E222">
+        <v>0.749</v>
+      </c>
+      <c r="F222">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
       <c r="A223" s="2">
-        <v>45325.7673611111</v>
+        <v>45325.76736111111</v>
       </c>
       <c r="B223">
         <v>0</v>
       </c>
-      <c r="C223" s="1">
+      <c r="C223">
         <v>0.254</v>
       </c>
-    </row>
-    <row r="224" spans="1:3">
+      <c r="D223">
+        <v>1.406</v>
+      </c>
+      <c r="E223">
+        <v>0.749</v>
+      </c>
+      <c r="F223">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
       <c r="A224" s="2">
-        <v>45325.7708333333</v>
+        <v>45325.77083333334</v>
       </c>
       <c r="B224">
         <v>0</v>
       </c>
-      <c r="C224" s="1">
+      <c r="C224">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="225" spans="1:3">
+      <c r="D224">
+        <v>1.408</v>
+      </c>
+      <c r="E224">
+        <v>0.75</v>
+      </c>
+      <c r="F224">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
       <c r="A225" s="2">
-        <v>45325.7743055556</v>
+        <v>45325.77430555555</v>
       </c>
       <c r="B225">
         <v>0</v>
       </c>
-      <c r="C225" s="1">
+      <c r="C225">
         <v>0.245</v>
       </c>
-    </row>
-    <row r="226" spans="1:3">
+      <c r="D225">
+        <v>1.408</v>
+      </c>
+      <c r="E225">
+        <v>0.751</v>
+      </c>
+      <c r="F225">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
       <c r="A226" s="2">
-        <v>45325.7777777778</v>
+        <v>45325.77777777778</v>
       </c>
       <c r="B226">
         <v>0</v>
       </c>
-      <c r="C226" s="1">
+      <c r="C226">
         <v>0.252</v>
       </c>
-    </row>
-    <row r="227" spans="1:3">
+      <c r="D226">
+        <v>1.407</v>
+      </c>
+      <c r="E226">
+        <v>0.75</v>
+      </c>
+      <c r="F226">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
       <c r="A227" s="2">
         <v>45325.78125</v>
       </c>
       <c r="B227">
         <v>0</v>
       </c>
-      <c r="C227" s="1">
+      <c r="C227">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="228" spans="1:3">
+      <c r="D227">
+        <v>1.408</v>
+      </c>
+      <c r="E227">
+        <v>0.751</v>
+      </c>
+      <c r="F227">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
       <c r="A228" s="2">
-        <v>45325.7847222222</v>
+        <v>45325.78472222222</v>
       </c>
       <c r="B228">
         <v>0</v>
       </c>
-      <c r="C228" s="1">
+      <c r="C228">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="229" spans="1:3">
+      <c r="D228">
+        <v>1.411</v>
+      </c>
+      <c r="E228">
+        <v>0.747</v>
+      </c>
+      <c r="F228">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
       <c r="A229" s="2">
-        <v>45325.7881944444</v>
+        <v>45325.78819444445</v>
       </c>
       <c r="B229">
         <v>0</v>
       </c>
-      <c r="C229" s="1">
+      <c r="C229">
         <v>0.252</v>
       </c>
-    </row>
-    <row r="230" spans="1:3">
+      <c r="D229">
+        <v>1.403</v>
+      </c>
+      <c r="E229">
+        <v>0.747</v>
+      </c>
+      <c r="F229">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
       <c r="A230" s="2">
-        <v>45325.7916666667</v>
+        <v>45325.79166666666</v>
       </c>
       <c r="B230">
         <v>0</v>
       </c>
-      <c r="C230" s="1">
+      <c r="C230">
         <v>0.249</v>
       </c>
-    </row>
-    <row r="231" spans="1:3">
+      <c r="D230">
+        <v>1.411</v>
+      </c>
+      <c r="E230">
+        <v>0.747</v>
+      </c>
+      <c r="F230">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
       <c r="A231" s="2">
-        <v>45325.7951388889</v>
+        <v>45325.79513888889</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
-      <c r="C231" s="1">
+      <c r="C231">
         <v>0.249</v>
       </c>
-    </row>
-    <row r="232" spans="1:3">
+      <c r="D231">
+        <v>1.412</v>
+      </c>
+      <c r="E231">
+        <v>0.748</v>
+      </c>
+      <c r="F231">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
       <c r="A232" s="2">
-        <v>45325.7986111111</v>
+        <v>45325.79861111111</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
-      <c r="C232" s="1">
+      <c r="C232">
         <v>0.249</v>
       </c>
-    </row>
-    <row r="233" spans="1:3">
+      <c r="D232">
+        <v>1.411</v>
+      </c>
+      <c r="E232">
+        <v>0.744</v>
+      </c>
+      <c r="F232">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
       <c r="A233" s="2">
-        <v>45325.8020833333</v>
+        <v>45325.80208333334</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
-      <c r="C233" s="1">
+      <c r="C233">
         <v>0.248</v>
       </c>
-    </row>
-    <row r="234" spans="1:3">
+      <c r="D233">
+        <v>1.41</v>
+      </c>
+      <c r="E233">
+        <v>0.75</v>
+      </c>
+      <c r="F233">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
       <c r="A234" s="2">
-        <v>45325.8055555556</v>
+        <v>45325.80555555555</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
-      <c r="C234" s="1">
+      <c r="C234">
         <v>0.249</v>
       </c>
-    </row>
-    <row r="235" spans="1:3">
+      <c r="D234">
+        <v>1.422</v>
+      </c>
+      <c r="E234">
+        <v>0.755</v>
+      </c>
+      <c r="F234">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
       <c r="A235" s="2">
-        <v>45325.8090277778</v>
+        <v>45325.80902777778</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
-      <c r="C235" s="1">
+      <c r="C235">
         <v>0.251</v>
       </c>
-    </row>
-    <row r="236" spans="1:3">
+      <c r="D235">
+        <v>1.423</v>
+      </c>
+      <c r="E235">
+        <v>0.766</v>
+      </c>
+      <c r="F235">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
       <c r="A236" s="2">
         <v>45325.8125</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
-      <c r="C236" s="1">
+      <c r="C236">
         <v>0.251</v>
       </c>
-    </row>
-    <row r="237" spans="1:3">
+      <c r="D236">
+        <v>1.423</v>
+      </c>
+      <c r="E236">
+        <v>0.763</v>
+      </c>
+      <c r="F236">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
       <c r="A237" s="2">
-        <v>45325.8159722222</v>
+        <v>45325.81597222222</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
-      <c r="C237" s="1">
+      <c r="C237">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="238" spans="1:3">
+      <c r="D237">
+        <v>1.422</v>
+      </c>
+      <c r="E237">
+        <v>0.766</v>
+      </c>
+      <c r="F237">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
       <c r="A238" s="2">
-        <v>45325.8194444444</v>
+        <v>45325.81944444445</v>
       </c>
       <c r="B238">
         <v>0</v>
       </c>
-      <c r="C238" s="1">
+      <c r="C238">
         <v>0.247</v>
       </c>
-    </row>
-    <row r="239" spans="1:3">
+      <c r="D238">
+        <v>1.42</v>
+      </c>
+      <c r="E238">
+        <v>0.763</v>
+      </c>
+      <c r="F238">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
       <c r="A239" s="2">
-        <v>45325.8229166667</v>
+        <v>45325.82291666666</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
-      <c r="C239" s="1">
+      <c r="C239">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="240" spans="1:3">
+      <c r="D239">
+        <v>1.422</v>
+      </c>
+      <c r="E239">
+        <v>0.765</v>
+      </c>
+      <c r="F239">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
       <c r="A240" s="2">
-        <v>45325.8263888889</v>
+        <v>45325.82638888889</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
-      <c r="C240" s="1">
+      <c r="C240">
         <v>0.247</v>
       </c>
-    </row>
-    <row r="241" spans="1:3">
+      <c r="D240">
+        <v>1.423</v>
+      </c>
+      <c r="E240">
+        <v>0.762</v>
+      </c>
+      <c r="F240">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
       <c r="A241" s="2">
-        <v>45325.8298611111</v>
+        <v>45325.82986111111</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
-      <c r="C241" s="1">
+      <c r="C241">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="242" spans="1:3">
+      <c r="D241">
+        <v>1.422</v>
+      </c>
+      <c r="E241">
+        <v>0.762</v>
+      </c>
+      <c r="F241">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
       <c r="A242" s="2">
-        <v>45325.8333333333</v>
+        <v>45325.83333333334</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
-      <c r="C242" s="1">
+      <c r="C242">
         <v>0.248</v>
       </c>
-    </row>
-    <row r="243" spans="1:3">
+      <c r="D242">
+        <v>1.424</v>
+      </c>
+      <c r="E242">
+        <v>0.763</v>
+      </c>
+      <c r="F242">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
       <c r="A243" s="2">
-        <v>45325.8368055556</v>
+        <v>45325.83680555555</v>
       </c>
       <c r="B243">
         <v>0</v>
       </c>
-      <c r="C243" s="1">
+      <c r="C243">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="244" spans="1:3">
+      <c r="D243">
+        <v>1.425</v>
+      </c>
+      <c r="E243">
+        <v>0.761</v>
+      </c>
+      <c r="F243">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
       <c r="A244" s="2">
-        <v>45325.8402777778</v>
+        <v>45325.84027777778</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
-      <c r="C244" s="1">
+      <c r="C244">
         <v>0.247</v>
       </c>
-    </row>
-    <row r="245" spans="1:3">
+      <c r="D244">
+        <v>1.43</v>
+      </c>
+      <c r="E244">
+        <v>0.762</v>
+      </c>
+      <c r="F244">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
       <c r="A245" s="2">
         <v>45325.84375</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
-      <c r="C245" s="1">
+      <c r="C245">
         <v>0.247</v>
       </c>
-    </row>
-    <row r="246" spans="1:3">
+      <c r="D245">
+        <v>1.423</v>
+      </c>
+      <c r="E245">
+        <v>0.763</v>
+      </c>
+      <c r="F245">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
       <c r="A246" s="2">
-        <v>45325.8472222222</v>
+        <v>45325.84722222222</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
-      <c r="C246" s="1">
+      <c r="C246">
         <v>0.249</v>
       </c>
-    </row>
-    <row r="247" spans="1:3">
+      <c r="D246">
+        <v>1.421</v>
+      </c>
+      <c r="E246">
+        <v>0.764</v>
+      </c>
+      <c r="F246">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
       <c r="A247" s="2">
-        <v>45325.8506944444</v>
+        <v>45325.85069444445</v>
       </c>
       <c r="B247">
         <v>0</v>
       </c>
-      <c r="C247" s="1">
+      <c r="C247">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="248" spans="1:3">
+      <c r="D247">
+        <v>1.422</v>
+      </c>
+      <c r="E247">
+        <v>0.761</v>
+      </c>
+      <c r="F247">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
       <c r="A248" s="2">
-        <v>45325.8541666667</v>
+        <v>45325.85416666666</v>
       </c>
       <c r="B248">
         <v>0</v>
       </c>
-      <c r="C248" s="1">
+      <c r="C248">
         <v>0.249</v>
       </c>
-    </row>
-    <row r="249" spans="1:3">
+      <c r="D248">
+        <v>1.421</v>
+      </c>
+      <c r="E248">
+        <v>0.764</v>
+      </c>
+      <c r="F248">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
       <c r="A249" s="2">
-        <v>45325.8576388889</v>
+        <v>45325.85763888889</v>
       </c>
       <c r="B249">
         <v>0</v>
       </c>
-      <c r="C249" s="1">
+      <c r="C249">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="250" spans="1:3">
+      <c r="D249">
+        <v>1.422</v>
+      </c>
+      <c r="E249">
+        <v>0.765</v>
+      </c>
+      <c r="F249">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
       <c r="A250" s="2">
-        <v>45325.8611111111</v>
+        <v>45325.86111111111</v>
       </c>
       <c r="B250">
         <v>0</v>
       </c>
-      <c r="C250" s="1">
+      <c r="C250">
         <v>0.248</v>
       </c>
-    </row>
-    <row r="251" spans="1:3">
+      <c r="D250">
+        <v>1.42</v>
+      </c>
+      <c r="E250">
+        <v>0.763</v>
+      </c>
+      <c r="F250">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
       <c r="A251" s="2">
-        <v>45325.8645833333</v>
+        <v>45325.86458333334</v>
       </c>
       <c r="B251">
         <v>0</v>
       </c>
-      <c r="C251" s="1">
+      <c r="C251">
         <v>0.252</v>
       </c>
-    </row>
-    <row r="252" spans="1:3">
+      <c r="D251">
+        <v>1.419</v>
+      </c>
+      <c r="E251">
+        <v>0.761</v>
+      </c>
+      <c r="F251">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
       <c r="A252" s="2">
-        <v>45325.8680555556</v>
+        <v>45325.86805555555</v>
       </c>
       <c r="B252">
         <v>0</v>
       </c>
-      <c r="C252" s="1">
+      <c r="C252">
         <v>0.249</v>
       </c>
-    </row>
-    <row r="253" spans="1:3">
+      <c r="D252">
+        <v>1.421</v>
+      </c>
+      <c r="E252">
+        <v>0.764</v>
+      </c>
+      <c r="F252">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
       <c r="A253" s="2">
-        <v>45325.8715277778</v>
+        <v>45325.87152777778</v>
       </c>
       <c r="B253">
         <v>0</v>
       </c>
-      <c r="C253" s="1">
+      <c r="C253">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="254" spans="1:3">
+      <c r="D253">
+        <v>1.418</v>
+      </c>
+      <c r="E253">
+        <v>0.761</v>
+      </c>
+      <c r="F253">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
       <c r="A254" s="2">
         <v>45325.875</v>
       </c>
       <c r="B254">
         <v>0</v>
       </c>
-      <c r="C254" s="1">
+      <c r="C254">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="255" spans="1:3">
+      <c r="D254">
+        <v>1.418</v>
+      </c>
+      <c r="E254">
+        <v>0.76</v>
+      </c>
+      <c r="F254">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
       <c r="A255" s="2">
-        <v>45325.8784722222</v>
+        <v>45325.87847222222</v>
       </c>
       <c r="B255">
         <v>0</v>
       </c>
-      <c r="C255" s="1">
+      <c r="C255">
         <v>0.249</v>
       </c>
-    </row>
-    <row r="256" spans="1:3">
+      <c r="D255">
+        <v>1.421</v>
+      </c>
+      <c r="E255">
+        <v>0.764</v>
+      </c>
+      <c r="F255">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
       <c r="A256" s="2">
-        <v>45325.8819444444</v>
+        <v>45325.88194444445</v>
       </c>
       <c r="B256">
         <v>0</v>
       </c>
-      <c r="C256" s="1">
+      <c r="C256">
         <v>0.247</v>
       </c>
-    </row>
-    <row r="257" spans="1:3">
+      <c r="D256">
+        <v>1.42</v>
+      </c>
+      <c r="E256">
+        <v>0.763</v>
+      </c>
+      <c r="F256">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" s="2">
-        <v>45325.8854166667</v>
+        <v>45325.88541666666</v>
       </c>
       <c r="B257">
         <v>0</v>
       </c>
-      <c r="C257" s="1">
+      <c r="C257">
         <v>0.249</v>
       </c>
-    </row>
-    <row r="258" spans="1:3">
+      <c r="D257">
+        <v>1.422</v>
+      </c>
+      <c r="E257">
+        <v>0.764</v>
+      </c>
+      <c r="F257">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258" s="2">
-        <v>45325.8888888889</v>
+        <v>45325.88888888889</v>
       </c>
       <c r="B258">
         <v>0</v>
       </c>
-      <c r="C258" s="1">
+      <c r="C258">
         <v>0.247</v>
       </c>
-    </row>
-    <row r="259" spans="1:3">
+      <c r="D258">
+        <v>1.419</v>
+      </c>
+      <c r="E258">
+        <v>0.762</v>
+      </c>
+      <c r="F258">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" s="2">
-        <v>45325.8923611111</v>
+        <v>45325.89236111111</v>
       </c>
       <c r="B259">
         <v>0</v>
       </c>
-      <c r="C259" s="1">
+      <c r="C259">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="260" spans="1:3">
+      <c r="D259">
+        <v>1.418</v>
+      </c>
+      <c r="E259">
+        <v>0.761</v>
+      </c>
+      <c r="F259">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" s="2">
-        <v>45325.8958333333</v>
+        <v>45325.89583333334</v>
       </c>
       <c r="B260">
         <v>0</v>
       </c>
-      <c r="C260" s="1">
+      <c r="C260">
         <v>0.247</v>
       </c>
-    </row>
-    <row r="261" spans="1:3">
+      <c r="D260">
+        <v>1.42</v>
+      </c>
+      <c r="E260">
+        <v>0.763</v>
+      </c>
+      <c r="F260">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261" s="2">
-        <v>45325.8993055556</v>
+        <v>45325.89930555555</v>
       </c>
       <c r="B261">
         <v>0</v>
       </c>
-      <c r="C261" s="1">
+      <c r="C261">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="262" spans="1:3">
+      <c r="D261">
+        <v>1.419</v>
+      </c>
+      <c r="E261">
+        <v>0.762</v>
+      </c>
+      <c r="F261">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" s="2">
-        <v>45325.9027777778</v>
+        <v>45325.90277777778</v>
       </c>
       <c r="B262">
         <v>0</v>
       </c>
-      <c r="C262" s="1">
+      <c r="C262">
         <v>0.245</v>
       </c>
-    </row>
-    <row r="263" spans="1:3">
+      <c r="D262">
+        <v>1.42</v>
+      </c>
+      <c r="E262">
+        <v>0.76</v>
+      </c>
+      <c r="F262">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263" s="2">
         <v>45325.90625</v>
       </c>
       <c r="B263">
         <v>0</v>
       </c>
-      <c r="C263" s="1">
+      <c r="C263">
         <v>0.237</v>
       </c>
-    </row>
-    <row r="264" spans="1:3">
+      <c r="D263">
+        <v>1.426</v>
+      </c>
+      <c r="E263">
+        <v>0.769</v>
+      </c>
+      <c r="F263">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" s="2">
-        <v>45325.9097222222</v>
+        <v>45325.90972222222</v>
       </c>
       <c r="B264">
         <v>0</v>
       </c>
-      <c r="C264" s="1">
+      <c r="C264">
         <v>0.245</v>
       </c>
-    </row>
-    <row r="265" spans="1:3">
+      <c r="D264">
+        <v>1.417</v>
+      </c>
+      <c r="E264">
+        <v>0.76</v>
+      </c>
+      <c r="F264">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265" s="2">
-        <v>45325.9131944444</v>
+        <v>45325.91319444445</v>
       </c>
       <c r="B265">
         <v>0</v>
       </c>
-      <c r="C265" s="1">
+      <c r="C265">
         <v>0.244</v>
       </c>
-    </row>
-    <row r="266" spans="1:3">
+      <c r="D265">
+        <v>1.416</v>
+      </c>
+      <c r="E265">
+        <v>0.76</v>
+      </c>
+      <c r="F265">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" s="2">
-        <v>45325.9166666667</v>
+        <v>45325.91666666666</v>
       </c>
       <c r="B266">
         <v>0</v>
       </c>
-      <c r="C266" s="1">
+      <c r="C266">
         <v>0.242</v>
       </c>
-    </row>
-    <row r="267" spans="1:3">
+      <c r="D266">
+        <v>1.42</v>
+      </c>
+      <c r="E266">
+        <v>0.757</v>
+      </c>
+      <c r="F266">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" s="2">
-        <v>45325.9201388889</v>
+        <v>45325.92013888889</v>
       </c>
       <c r="B267">
         <v>0</v>
       </c>
-      <c r="C267" s="1">
+      <c r="C267">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="268" spans="1:3">
+      <c r="D267">
+        <v>1.423</v>
+      </c>
+      <c r="E267">
+        <v>0.756</v>
+      </c>
+      <c r="F267">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" s="2">
-        <v>45325.9236111111</v>
+        <v>45325.92361111111</v>
       </c>
       <c r="B268">
         <v>0</v>
       </c>
-      <c r="C268" s="1">
+      <c r="C268">
         <v>0.241</v>
       </c>
-    </row>
-    <row r="269" spans="1:3">
+      <c r="D268">
+        <v>1.423</v>
+      </c>
+      <c r="E268">
+        <v>0.756</v>
+      </c>
+      <c r="F268">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" s="2">
-        <v>45325.9270833333</v>
+        <v>45325.92708333334</v>
       </c>
       <c r="B269">
         <v>0</v>
       </c>
-      <c r="C269" s="1">
+      <c r="C269">
         <v>0.242</v>
       </c>
-    </row>
-    <row r="270" spans="1:3">
+      <c r="D269">
+        <v>1.414</v>
+      </c>
+      <c r="E269">
+        <v>0.757</v>
+      </c>
+      <c r="F269">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270" s="2">
-        <v>45325.9305555556</v>
+        <v>45325.93055555555</v>
       </c>
       <c r="B270">
         <v>0</v>
       </c>
-      <c r="C270" s="1">
+      <c r="C270">
         <v>0.243</v>
       </c>
-    </row>
-    <row r="271" spans="1:3">
+      <c r="D270">
+        <v>1.415</v>
+      </c>
+      <c r="E270">
+        <v>0.758</v>
+      </c>
+      <c r="F270">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" s="2">
-        <v>45325.9340277778</v>
+        <v>45325.93402777778</v>
       </c>
       <c r="B271">
         <v>0</v>
       </c>
-      <c r="C271" s="1">
+      <c r="C271">
         <v>0.242</v>
       </c>
-    </row>
-    <row r="272" spans="1:3">
+      <c r="D271">
+        <v>1.414</v>
+      </c>
+      <c r="E271">
+        <v>0.757</v>
+      </c>
+      <c r="F271">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272" s="2">
         <v>45325.9375</v>
       </c>
       <c r="B272">
         <v>0</v>
       </c>
-      <c r="C272" s="1">
+      <c r="C272">
         <v>0.242</v>
       </c>
-    </row>
-    <row r="273" spans="1:3">
+      <c r="D272">
+        <v>1.415</v>
+      </c>
+      <c r="E272">
+        <v>0.758</v>
+      </c>
+      <c r="F272">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
       <c r="A273" s="2">
-        <v>45325.9409722222</v>
+        <v>45325.94097222222</v>
       </c>
       <c r="B273">
         <v>0</v>
       </c>
-      <c r="C273" s="1">
+      <c r="C273">
         <v>0.242</v>
       </c>
-    </row>
-    <row r="274" spans="1:3">
+      <c r="D273">
+        <v>1.415</v>
+      </c>
+      <c r="E273">
+        <v>0.757</v>
+      </c>
+      <c r="F273">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
       <c r="A274" s="2">
-        <v>45325.9444444444</v>
+        <v>45325.94444444445</v>
       </c>
       <c r="B274">
         <v>0</v>
       </c>
-      <c r="C274" s="1">
+      <c r="C274">
         <v>0.238</v>
       </c>
-    </row>
-    <row r="275" spans="1:3">
+      <c r="D274">
+        <v>1.417</v>
+      </c>
+      <c r="E274">
+        <v>0.76</v>
+      </c>
+      <c r="F274">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
       <c r="A275" s="2">
-        <v>45325.9479166667</v>
+        <v>45325.94791666666</v>
       </c>
       <c r="B275">
         <v>0</v>
       </c>
-      <c r="C275" s="1">
+      <c r="C275">
         <v>0.233</v>
       </c>
-    </row>
-    <row r="276" spans="1:3">
+      <c r="D275">
+        <v>1.416</v>
+      </c>
+      <c r="E275">
+        <v>0.759</v>
+      </c>
+      <c r="F275">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
       <c r="A276" s="2">
-        <v>45325.9513888889</v>
+        <v>45325.95138888889</v>
       </c>
       <c r="B276">
         <v>0</v>
       </c>
-      <c r="C276" s="1">
+      <c r="C276">
         <v>0.235</v>
       </c>
-    </row>
-    <row r="277" spans="1:3">
+      <c r="D276">
+        <v>1.418</v>
+      </c>
+      <c r="E276">
+        <v>0.761</v>
+      </c>
+      <c r="F276">
+        <v>0.103</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
       <c r="A277" s="2">
-        <v>45325.9548611111</v>
+        <v>45325.95486111111</v>
       </c>
       <c r="B277">
         <v>0</v>
       </c>
-      <c r="C277" s="1">
+      <c r="C277">
         <v>0.238</v>
       </c>
-    </row>
-    <row r="278" spans="1:3">
+      <c r="D277">
+        <v>1.42</v>
+      </c>
+      <c r="E277">
+        <v>0.753</v>
+      </c>
+      <c r="F277">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
       <c r="A278" s="2">
-        <v>45325.9583333333</v>
+        <v>45325.95833333334</v>
       </c>
       <c r="B278">
         <v>0</v>
       </c>
-      <c r="C278" s="1">
+      <c r="C278">
         <v>0.237</v>
       </c>
-    </row>
-    <row r="279" spans="1:3">
+      <c r="D278">
+        <v>1.419</v>
+      </c>
+      <c r="E278">
+        <v>0.762</v>
+      </c>
+      <c r="F278">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
       <c r="A279" s="2">
-        <v>45325.9618055556</v>
+        <v>45325.96180555555</v>
       </c>
       <c r="B279">
         <v>0</v>
       </c>
-      <c r="C279" s="1">
+      <c r="C279">
         <v>0.236</v>
       </c>
-    </row>
-    <row r="280" spans="1:3">
+      <c r="D279">
+        <v>1.419</v>
+      </c>
+      <c r="E279">
+        <v>0.762</v>
+      </c>
+      <c r="F279">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" s="2">
-        <v>45325.9652777778</v>
+        <v>45325.96527777778</v>
       </c>
       <c r="B280">
         <v>0</v>
       </c>
-      <c r="C280" s="1">
+      <c r="C280">
         <v>0.236</v>
       </c>
-    </row>
-    <row r="281" spans="1:3">
+      <c r="D280">
+        <v>1.419</v>
+      </c>
+      <c r="E280">
+        <v>0.762</v>
+      </c>
+      <c r="F280">
+        <v>0.103</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" s="2">
         <v>45325.96875</v>
       </c>
       <c r="B281">
         <v>0</v>
       </c>
-      <c r="C281" s="1">
+      <c r="C281">
         <v>0.236</v>
       </c>
-    </row>
-    <row r="282" spans="1:3">
+      <c r="D281">
+        <v>1.418</v>
+      </c>
+      <c r="E281">
+        <v>0.761</v>
+      </c>
+      <c r="F281">
+        <v>0.103</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282" s="2">
-        <v>45325.9722222222</v>
+        <v>45325.97222222222</v>
       </c>
       <c r="B282">
         <v>0</v>
       </c>
-      <c r="C282" s="1">
+      <c r="C282">
         <v>0.235</v>
       </c>
-    </row>
-    <row r="283" spans="1:3">
+      <c r="D282">
+        <v>1.418</v>
+      </c>
+      <c r="E282">
+        <v>0.757</v>
+      </c>
+      <c r="F282">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
       <c r="A283" s="2">
-        <v>45325.9756944444</v>
+        <v>45325.97569444445</v>
       </c>
       <c r="B283">
         <v>0</v>
       </c>
-      <c r="C283" s="1">
+      <c r="C283">
         <v>0.236</v>
       </c>
-    </row>
-    <row r="284" spans="1:3">
+      <c r="D283">
+        <v>1.416</v>
+      </c>
+      <c r="E283">
+        <v>0.751</v>
+      </c>
+      <c r="F283">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284" s="2">
-        <v>45325.9791666667</v>
+        <v>45325.97916666666</v>
       </c>
       <c r="B284">
         <v>0</v>
       </c>
-      <c r="C284" s="1">
+      <c r="C284">
         <v>0.237</v>
       </c>
-    </row>
-    <row r="285" spans="1:3">
+      <c r="D284">
+        <v>1.419</v>
+      </c>
+      <c r="E284">
+        <v>0.756</v>
+      </c>
+      <c r="F284">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
       <c r="A285" s="2">
-        <v>45325.9826388889</v>
+        <v>45325.98263888889</v>
       </c>
       <c r="B285">
         <v>0</v>
       </c>
-      <c r="C285" s="1">
+      <c r="C285">
         <v>0.232</v>
       </c>
-    </row>
-    <row r="286" spans="1:3">
+      <c r="D285">
+        <v>1.418</v>
+      </c>
+      <c r="E285">
+        <v>0.754</v>
+      </c>
+      <c r="F285">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
       <c r="A286" s="2">
-        <v>45325.9861111111</v>
+        <v>45325.98611111111</v>
       </c>
       <c r="B286">
         <v>0</v>
       </c>
-      <c r="C286" s="1">
+      <c r="C286">
         <v>0.234</v>
       </c>
-    </row>
-    <row r="287" spans="1:3">
+      <c r="D286">
+        <v>1.416</v>
+      </c>
+      <c r="E286">
+        <v>0.76</v>
+      </c>
+      <c r="F286">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
       <c r="A287" s="2">
-        <v>45325.9895833333</v>
+        <v>45325.98958333334</v>
       </c>
       <c r="B287">
         <v>0</v>
       </c>
-      <c r="C287" s="1">
+      <c r="C287">
         <v>0.234</v>
       </c>
-    </row>
-    <row r="288" spans="1:3">
+      <c r="D287">
+        <v>1.416</v>
+      </c>
+      <c r="E287">
+        <v>0.749</v>
+      </c>
+      <c r="F287">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
       <c r="A288" s="2">
-        <v>45325.9930555556</v>
+        <v>45325.99305555555</v>
       </c>
       <c r="B288">
         <v>0</v>
       </c>
-      <c r="C288" s="1">
+      <c r="C288">
         <v>0.235</v>
       </c>
-    </row>
-    <row r="289" spans="1:3">
+      <c r="D288">
+        <v>1.418</v>
+      </c>
+      <c r="E288">
+        <v>0.751</v>
+      </c>
+      <c r="F288">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
       <c r="A289" s="2">
-        <v>45325.9965277778</v>
+        <v>45325.99652777778</v>
       </c>
       <c r="B289">
         <v>0</v>
       </c>
-      <c r="C289" s="1">
+      <c r="C289">
         <v>0.236</v>
       </c>
+      <c r="D289">
+        <v>1.412</v>
+      </c>
+      <c r="E289">
+        <v>0.752</v>
+      </c>
+      <c r="F289">
+        <v>0.103</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>